--- a/data/processed/composite_master_quarterly.xlsx
+++ b/data/processed/composite_master_quarterly.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,224 +417,224 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FY_Quarter</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDP_growth_old</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GFCE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PFCE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>GFCF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Exports</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Imports</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>NetExports</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FiscalDeficit_pct_GDP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Repo_QtrAvg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>CPI_Inflation</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>IIP_growth</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>INR_USD</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>INR_USD_vol</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Brent_USD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>M3_level</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>GDP_level_old</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>GDP_level_new</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>GDP_growth_new</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>base_year_target</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>has_new_base</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>GFCF_YoY</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Exports_YoY</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Imports_YoY</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>M3_level_YoY</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>RealRate</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>CrudeINR</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>CrudeINR_YoY</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>M3_growth_YoY</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>RealM3_YoY</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>GDP_proxy_old</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>InvestmentRate</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>TradeOpenness</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>COVID</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>BaseRevision_gap</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>GDP_growth</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>GDP_growth_source</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>GDP_growth_lag1</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>GDP_growth_lag4</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>BankCredit_YoY</t>
         </is>
       </c>
     </row>
@@ -700,39 +688,37 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
+      <c r="Z2" t="n">
         <v>5247.091272</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>2000784.9</v>
+      </c>
       <c r="AE2" t="n">
-        <v>2000784.9</v>
+        <v>34.83406936947595</v>
       </c>
       <c r="AF2" t="n">
-        <v>34.83406936947595</v>
+        <v>57.51108977281867</v>
       </c>
       <c r="AG2" t="n">
-        <v>57.51108977281867</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -743,18 +729,18 @@
       <c r="AL2" t="n">
         <v>0</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>20.68093134213473</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,42 +792,40 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
+      <c r="Z3" t="n">
         <v>5188.316065999999</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1978744.1</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1978744.1</v>
+        <v>36.77832317983917</v>
       </c>
       <c r="AF3" t="n">
-        <v>36.77832317983917</v>
+        <v>58.00764232221842</v>
       </c>
       <c r="AG3" t="n">
-        <v>58.00764232221842</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -849,18 +833,18 @@
       <c r="AL3" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>19.54897231033894</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -912,61 +896,59 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
+      <c r="Z4" t="n">
         <v>5571.615992</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>2077054.9</v>
+      </c>
       <c r="AE4" t="n">
-        <v>2077054.9</v>
+        <v>36.21289451713577</v>
       </c>
       <c r="AF4" t="n">
-        <v>36.21289451713577</v>
+        <v>61.02004333154603</v>
       </c>
       <c r="AG4" t="n">
-        <v>61.02004333154603</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>15.97466886934438</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1020,38 +1002,36 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>0.7199999999999998</v>
+      </c>
       <c r="Z5" t="n">
-        <v>0.7199999999999998</v>
-      </c>
-      <c r="AA5" t="n">
         <v>5957.187441333333</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>2248347.9</v>
+      </c>
       <c r="AE5" t="n">
-        <v>2248347.9</v>
+        <v>36.5097945918423</v>
       </c>
       <c r="AF5" t="n">
-        <v>36.5097945918423</v>
+        <v>57.53421434467503</v>
       </c>
       <c r="AG5" t="n">
-        <v>57.53421434467503</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1060,23 +1040,23 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>16.99023695512736</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1134,55 +1114,53 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T6" t="n">
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>9.575513361842125</v>
       </c>
       <c r="V6" t="n">
-        <v>9.575513361842125</v>
+        <v>5.111637788934331</v>
       </c>
       <c r="W6" t="n">
-        <v>5.111637788934331</v>
+        <v>5.267624749866529</v>
       </c>
       <c r="X6" t="n">
-        <v>5.267624749866529</v>
+        <v>15.82326235219023</v>
       </c>
       <c r="Y6" t="n">
+        <v>-1.814444444444446</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5865.912661111111</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>11.79360824945666</v>
+      </c>
+      <c r="AB6" t="n">
         <v>15.82326235219023</v>
       </c>
-      <c r="Z6" t="n">
-        <v>-1.814444444444446</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5865.912661111111</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11.79360824945666</v>
-      </c>
       <c r="AC6" t="n">
-        <v>15.82326235219023</v>
+        <v>5.919929018856893</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.919929018856893</v>
+        <v>2072727.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>2072727.7</v>
+        <v>36.84477222936713</v>
       </c>
       <c r="AF6" t="n">
-        <v>36.84477222936713</v>
+        <v>58.40109629451084</v>
       </c>
       <c r="AG6" t="n">
-        <v>58.40109629451084</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1193,20 +1171,20 @@
       <c r="AL6" t="n">
         <v>0</v>
       </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
         <v>4.87</v>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>19.04844621955139</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1264,58 +1242,56 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T7" t="n">
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.42578628425272</v>
       </c>
       <c r="V7" t="n">
-        <v>5.42578628425272</v>
+        <v>28.60116106573245</v>
       </c>
       <c r="W7" t="n">
-        <v>28.60116106573245</v>
+        <v>16.35569848350134</v>
       </c>
       <c r="X7" t="n">
-        <v>16.35569848350134</v>
+        <v>13.63341342336888</v>
       </c>
       <c r="Y7" t="n">
+        <v>-2.026666666666666</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6052.851920444445</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>16.66313006853821</v>
+      </c>
+      <c r="AB7" t="n">
         <v>13.63341342336888</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-2.026666666666666</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6052.851920444445</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16.66313006853821</v>
-      </c>
       <c r="AC7" t="n">
-        <v>13.63341342336888</v>
+        <v>3.606746756702213</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.606746756702213</v>
+        <v>2185184.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>2185184.4</v>
+        <v>35.11076685336029</v>
       </c>
       <c r="AF7" t="n">
-        <v>35.11076685336029</v>
+        <v>63.96095908427682</v>
       </c>
       <c r="AG7" t="n">
-        <v>63.96095908427682</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1323,22 +1299,22 @@
       <c r="AL7" t="n">
         <v>0</v>
       </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
         <v>7.49</v>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AP7" t="n">
         <v>4.87</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>16.33561091824198</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1396,81 +1372,79 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T8" t="n">
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.283711069042749</v>
       </c>
       <c r="V8" t="n">
-        <v>2.283711069042749</v>
+        <v>-4.49552591945932</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.49552591945932</v>
+        <v>3.097123125456802</v>
       </c>
       <c r="X8" t="n">
-        <v>3.097123125456802</v>
+        <v>11.24888299217723</v>
       </c>
       <c r="Y8" t="n">
+        <v>-1.763333333333334</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5961.101261111111</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.990526082026349</v>
+      </c>
+      <c r="AB8" t="n">
         <v>11.24888299217723</v>
       </c>
-      <c r="Z8" t="n">
-        <v>-1.763333333333334</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5961.101261111111</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6.990526082026349</v>
-      </c>
       <c r="AC8" t="n">
-        <v>11.24888299217723</v>
+        <v>1.485549658843899</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.485549658843899</v>
+        <v>2128943.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2128943.1</v>
+        <v>36.13712832437842</v>
       </c>
       <c r="AF8" t="n">
-        <v>36.13712832437842</v>
+        <v>59.40262565025811</v>
       </c>
       <c r="AG8" t="n">
-        <v>59.40262565025811</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
         <v>5.38</v>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AP8" t="n">
         <v>7.49</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>15.09073998649066</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1528,52 +1502,50 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T9" t="n">
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.004176558644334</v>
       </c>
       <c r="V9" t="n">
-        <v>3.004176558644334</v>
+        <v>-0.03185422286192674</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03185422286192674</v>
+        <v>0.3793396929364645</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3793396929364645</v>
+        <v>13.91723013647719</v>
       </c>
       <c r="Y9" t="n">
+        <v>-2.106344086021505</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6093.205149777778</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.283253796929396</v>
+      </c>
+      <c r="AB9" t="n">
         <v>13.91723013647719</v>
       </c>
-      <c r="Z9" t="n">
-        <v>-2.106344086021505</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6093.205149777778</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.283253796929396</v>
-      </c>
       <c r="AC9" t="n">
-        <v>13.91723013647719</v>
+        <v>4.02056346981052</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.02056346981052</v>
+        <v>2323049.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>2323049.3</v>
+        <v>36.39731192962629</v>
       </c>
       <c r="AF9" t="n">
-        <v>36.39731192962629</v>
+        <v>55.79331872121698</v>
       </c>
       <c r="AG9" t="n">
-        <v>55.79331872121698</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1582,27 +1554,27 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AP9" t="n">
         <v>5.38</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>14.06391082060408</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1660,55 +1632,53 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T10" t="n">
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.858888886851996</v>
       </c>
       <c r="V10" t="n">
-        <v>2.858888886851996</v>
+        <v>3.294761157642023</v>
       </c>
       <c r="W10" t="n">
-        <v>3.294761157642023</v>
+        <v>-3.00363159040995</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.00363159040995</v>
+        <v>12.69099146058279</v>
       </c>
       <c r="Y10" t="n">
+        <v>-1.471290322580646</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5736.900974888889</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.199345501298089</v>
+      </c>
+      <c r="AB10" t="n">
         <v>12.69099146058279</v>
       </c>
-      <c r="Z10" t="n">
-        <v>-1.471290322580646</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5736.900974888889</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-2.199345501298089</v>
-      </c>
       <c r="AC10" t="n">
-        <v>12.69099146058279</v>
+        <v>3.88099146058279</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.88099146058279</v>
+        <v>2272050.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2272050.6</v>
+        <v>34.57338934264932</v>
       </c>
       <c r="AF10" t="n">
-        <v>34.57338934264932</v>
+        <v>53.15432675663122</v>
       </c>
       <c r="AG10" t="n">
-        <v>53.15432675663122</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -1719,23 +1689,23 @@
       <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
         <v>6.45</v>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP10" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AQ10" t="n">
-        <v>4.3</v>
+        <v>4.87</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.87</v>
+        <v>13.4687945083054</v>
       </c>
     </row>
     <row r="11">
@@ -1794,58 +1764,56 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T11" t="n">
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.620768082790791</v>
       </c>
       <c r="V11" t="n">
-        <v>1.620768082790791</v>
+        <v>-1.099745006218456</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.099745006218456</v>
+        <v>-8.164754685887843</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.164754685887843</v>
+        <v>13.0042499150413</v>
       </c>
       <c r="Y11" t="n">
+        <v>-2.809444444444444</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6863.803933666666</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>13.39784987111787</v>
+      </c>
+      <c r="AB11" t="n">
         <v>13.0042499150413</v>
       </c>
-      <c r="Z11" t="n">
-        <v>-2.809444444444444</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6863.803933666666</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13.39784987111787</v>
-      </c>
       <c r="AC11" t="n">
-        <v>13.0042499150413</v>
+        <v>2.914249915041299</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.914249915041299</v>
+        <v>2318883.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2318883.3</v>
+        <v>33.62265362814938</v>
       </c>
       <c r="AF11" t="n">
-        <v>33.62265362814938</v>
+        <v>57.33926325658562</v>
       </c>
       <c r="AG11" t="n">
-        <v>57.33926325658562</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -1853,23 +1821,23 @@
       <c r="AL11" t="n">
         <v>0</v>
       </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
         <v>7.34</v>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP11" t="n">
+        <v>6.45</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>6.45</v>
+        <v>7.49</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.49</v>
+        <v>17.59710763661637</v>
       </c>
     </row>
     <row r="12">
@@ -1928,82 +1896,80 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T12" t="n">
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.370827732745595</v>
       </c>
       <c r="V12" t="n">
-        <v>2.370827732745595</v>
+        <v>16.12191446918512</v>
       </c>
       <c r="W12" t="n">
-        <v>16.12191446918512</v>
+        <v>-14.06065989558057</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.06065989558057</v>
+        <v>14.80433839943327</v>
       </c>
       <c r="Y12" t="n">
+        <v>-2.918602150537635</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6776.804489666667</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>13.68376735817291</v>
+      </c>
+      <c r="AB12" t="n">
         <v>14.80433839943327</v>
       </c>
-      <c r="Z12" t="n">
-        <v>-2.918602150537635</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6776.804489666667</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.68376735817291</v>
-      </c>
       <c r="AC12" t="n">
-        <v>14.80433839943327</v>
+        <v>4.211005066099936</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.211005066099936</v>
+        <v>2437481</v>
       </c>
       <c r="AE12" t="n">
-        <v>2437481</v>
+        <v>32.31116878449514</v>
       </c>
       <c r="AF12" t="n">
-        <v>32.31116878449514</v>
+        <v>51.13394935181033</v>
       </c>
       <c r="AG12" t="n">
-        <v>51.13394935181033</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="n">
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
         <v>6.53</v>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP12" t="n">
+        <v>7.34</v>
+      </c>
       <c r="AQ12" t="n">
-        <v>7.34</v>
+        <v>5.38</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.38</v>
+        <v>14.23574573868303</v>
       </c>
     </row>
     <row r="13">
@@ -2062,52 +2028,50 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T13" t="n">
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.3993719896750902</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3993719896750902</v>
+        <v>14.37529254566316</v>
       </c>
       <c r="W13" t="n">
-        <v>14.37529254566316</v>
+        <v>-6.919657925902833</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.919657925902833</v>
+        <v>13.43971225818972</v>
       </c>
       <c r="Y13" t="n">
+        <v>-0.315913978494625</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6682.680888888889</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9.674313019521573</v>
+      </c>
+      <c r="AB13" t="n">
         <v>13.43971225818972</v>
       </c>
-      <c r="Z13" t="n">
-        <v>-0.315913978494625</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6682.680888888889</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.674313019521573</v>
-      </c>
       <c r="AC13" t="n">
-        <v>13.43971225818972</v>
+        <v>5.196378924856385</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.196378924856385</v>
+        <v>2527377.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>2527377.6</v>
+        <v>33.32112700531966</v>
       </c>
       <c r="AF13" t="n">
-        <v>33.32112700531966</v>
+        <v>52.58889688663855</v>
       </c>
       <c r="AG13" t="n">
-        <v>52.58889688663855</v>
+        <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2116,28 +2080,28 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
         <v>5.34</v>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP13" t="n">
+        <v>6.53</v>
+      </c>
       <c r="AQ13" t="n">
-        <v>6.53</v>
+        <v>4.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>13.94625906295703</v>
       </c>
     </row>
     <row r="14">
@@ -2196,55 +2160,53 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T14" t="n">
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.933630748051397</v>
       </c>
       <c r="V14" t="n">
-        <v>2.933630748051397</v>
+        <v>13.11119259760236</v>
       </c>
       <c r="W14" t="n">
-        <v>13.11119259760236</v>
+        <v>0.8886256825372474</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8886256825372474</v>
+        <v>11.82382177147869</v>
       </c>
       <c r="Y14" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6559.778436666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14.34358838298957</v>
+      </c>
+      <c r="AB14" t="n">
         <v>11.82382177147869</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0.1400000000000006</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6559.778436666667</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>14.34358838298957</v>
-      </c>
       <c r="AC14" t="n">
-        <v>11.82382177147869</v>
+        <v>3.963821771478694</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.963821771478694</v>
+        <v>2463577.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2463577.7</v>
+        <v>32.82093761442961</v>
       </c>
       <c r="AF14" t="n">
-        <v>32.82093761442961</v>
+        <v>52.18790135987997</v>
       </c>
       <c r="AG14" t="n">
-        <v>52.18790135987997</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2255,23 +2217,23 @@
       <c r="AL14" t="n">
         <v>0</v>
       </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="n">
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
         <v>8.02</v>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP14" t="n">
+        <v>5.34</v>
+      </c>
       <c r="AQ14" t="n">
-        <v>5.34</v>
+        <v>6.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.45</v>
+        <v>12.77406130657064</v>
       </c>
     </row>
     <row r="15">
@@ -2330,58 +2292,56 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T15" t="n">
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.602343991388147</v>
       </c>
       <c r="V15" t="n">
-        <v>4.602343991388147</v>
+        <v>-2.869419997361555</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.869419997361555</v>
+        <v>-0.4208734903458744</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4208734903458744</v>
+        <v>12.43756629597852</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.316666666666666</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6171.128698777778</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-10.09171068379947</v>
+      </c>
+      <c r="AB15" t="n">
         <v>12.43756629597852</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.316666666666666</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>6171.128698777778</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-10.09171068379947</v>
-      </c>
       <c r="AC15" t="n">
-        <v>12.43756629597852</v>
+        <v>5.754232962645187</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.754232962645187</v>
+        <v>2480862.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>2480862.6</v>
+        <v>32.87377543601165</v>
       </c>
       <c r="AF15" t="n">
-        <v>32.87377543601165</v>
+        <v>52.73325092651241</v>
       </c>
       <c r="AG15" t="n">
-        <v>52.73325092651241</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2389,23 +2349,23 @@
       <c r="AL15" t="n">
         <v>0</v>
       </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="n">
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP15" t="n">
+        <v>8.02</v>
+      </c>
       <c r="AQ15" t="n">
-        <v>8.02</v>
+        <v>7.34</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.34</v>
+        <v>9.211775467878791</v>
       </c>
     </row>
     <row r="16">
@@ -2464,82 +2424,80 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T16" t="n">
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.7692057656213613</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7692057656213613</v>
+        <v>3.502283006831108</v>
       </c>
       <c r="W16" t="n">
-        <v>3.502283006831108</v>
+        <v>7.605123275071479</v>
       </c>
       <c r="X16" t="n">
-        <v>7.605123275071479</v>
+        <v>10.71072906091495</v>
       </c>
       <c r="Y16" t="n">
+        <v>3.943333333333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4731.892736888889</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-30.17516228918626</v>
+      </c>
+      <c r="AB16" t="n">
         <v>10.71072906091495</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.943333333333333</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4731.892736888889</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-30.17516228918626</v>
-      </c>
       <c r="AC16" t="n">
-        <v>10.71072906091495</v>
+        <v>6.65406239424828</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.65406239424828</v>
+        <v>2504877.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>2504877.3</v>
+        <v>31.6836557223781</v>
       </c>
       <c r="AF16" t="n">
-        <v>31.6836557223781</v>
+        <v>52.5368727641869</v>
       </c>
       <c r="AG16" t="n">
-        <v>52.5368727641869</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="n">
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="n">
         <v>5.92</v>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP16" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="AQ16" t="n">
-        <v>8.699999999999999</v>
+        <v>6.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.53</v>
+        <v>10.05307330780989</v>
       </c>
     </row>
     <row r="17">
@@ -2598,52 +2556,50 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T17" t="n">
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.159494731762379</v>
       </c>
       <c r="V17" t="n">
-        <v>2.159494731762379</v>
+        <v>-4.744519677206238</v>
       </c>
       <c r="W17" t="n">
-        <v>-4.744519677206238</v>
+        <v>-4.182339733287</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.182339733287</v>
+        <v>10.85152572374752</v>
       </c>
       <c r="Y17" t="n">
+        <v>2.442365591397849</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3355.652919444444</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-49.78582734627062</v>
+      </c>
+      <c r="AB17" t="n">
         <v>10.85152572374752</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.442365591397849</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3355.652919444444</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-49.78582734627062</v>
-      </c>
       <c r="AC17" t="n">
-        <v>10.85152572374752</v>
+        <v>5.581525723747524</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.581525723747524</v>
+        <v>2640135.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>2640135.4</v>
+        <v>32.58684762910266</v>
       </c>
       <c r="AF17" t="n">
-        <v>32.58684762910266</v>
+        <v>48.09703320519091</v>
       </c>
       <c r="AG17" t="n">
-        <v>48.09703320519091</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2652,28 +2608,28 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="n">
         <v>7.11</v>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP17" t="n">
+        <v>5.92</v>
+      </c>
       <c r="AQ17" t="n">
-        <v>5.92</v>
+        <v>5.34</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.34</v>
+        <v>9.047647923575219</v>
       </c>
     </row>
     <row r="18">
@@ -2732,55 +2688,53 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T18" t="n">
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.677223461241952</v>
       </c>
       <c r="V18" t="n">
-        <v>3.677223461241952</v>
+        <v>-6.429572715533838</v>
       </c>
       <c r="W18" t="n">
-        <v>-6.429572715533838</v>
+        <v>-5.775424759376779</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.775424759376779</v>
+        <v>10.61103602271594</v>
       </c>
       <c r="Y18" t="n">
+        <v>2.326111111111111</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3915.762237333333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-40.30648633731726</v>
+      </c>
+      <c r="AB18" t="n">
         <v>10.61103602271594</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.326111111111111</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3915.762237333333</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-40.30648633731726</v>
-      </c>
       <c r="AC18" t="n">
-        <v>10.61103602271594</v>
+        <v>5.517702689382602</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.517702689382602</v>
+        <v>2605637.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2605637.4</v>
+        <v>32.17263461140065</v>
       </c>
       <c r="AF18" t="n">
-        <v>32.17263461140065</v>
+        <v>46.33658927370325</v>
       </c>
       <c r="AG18" t="n">
-        <v>46.33658927370325</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -2791,23 +2745,23 @@
       <c r="AL18" t="n">
         <v>0</v>
       </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="n">
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
         <v>7.59</v>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP18" t="n">
+        <v>7.11</v>
+      </c>
       <c r="AQ18" t="n">
-        <v>7.11</v>
+        <v>8.02</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.02</v>
+        <v>8.788918414916846</v>
       </c>
     </row>
     <row r="19">
@@ -2866,58 +2820,56 @@
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T19" t="n">
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.532117831185033</v>
       </c>
       <c r="V19" t="n">
-        <v>3.532117831185033</v>
+        <v>-4.741623456412802</v>
       </c>
       <c r="W19" t="n">
-        <v>-4.741623456412802</v>
+        <v>-3.629079934995072</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.629079934995072</v>
+        <v>10.65871462781398</v>
       </c>
       <c r="Y19" t="n">
+        <v>3.292222222222223</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3263.912507777777</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-47.10995885689096</v>
+      </c>
+      <c r="AB19" t="n">
         <v>10.65871462781398</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.292222222222223</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3263.912507777777</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-47.10995885689096</v>
-      </c>
       <c r="AC19" t="n">
-        <v>10.65871462781398</v>
+        <v>6.712047961147315</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.712047961147315</v>
+        <v>2632744.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2632744.4</v>
+        <v>32.07145744949643</v>
       </c>
       <c r="AF19" t="n">
-        <v>32.07145744949643</v>
+        <v>47.62298991121205</v>
       </c>
       <c r="AG19" t="n">
-        <v>47.62298991121205</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -2925,23 +2877,23 @@
       <c r="AL19" t="n">
         <v>0</v>
       </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="n">
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP19" t="n">
+        <v>7.59</v>
+      </c>
       <c r="AQ19" t="n">
-        <v>7.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.699999999999999</v>
+        <v>9.281122610061022</v>
       </c>
     </row>
     <row r="20">
@@ -3000,82 +2952,80 @@
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T20" t="n">
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>10.23364972915188</v>
       </c>
       <c r="V20" t="n">
-        <v>10.23364972915188</v>
+        <v>-8.870003053492791</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.870003053492791</v>
+        <v>-9.743196979576163</v>
       </c>
       <c r="X20" t="n">
-        <v>-9.743196979576163</v>
+        <v>10.71061117661882</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2872.288347333334</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-39.29937749979943</v>
+      </c>
+      <c r="AB20" t="n">
         <v>10.71061117661882</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2872.288347333334</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-39.29937749979943</v>
-      </c>
       <c r="AC20" t="n">
-        <v>10.71061117661882</v>
+        <v>5.370611176618823</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.370611176618823</v>
+        <v>2745756.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>2745756.2</v>
+        <v>31.86206772473098</v>
       </c>
       <c r="AF20" t="n">
-        <v>31.86206772473098</v>
+        <v>43.46026788540075</v>
       </c>
       <c r="AG20" t="n">
-        <v>43.46026788540075</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="n">
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP20" t="n">
+        <v>8.029999999999999</v>
+      </c>
       <c r="AQ20" t="n">
-        <v>8.029999999999999</v>
+        <v>5.92</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.92</v>
+        <v>10.59938609872986</v>
       </c>
     </row>
     <row r="21">
@@ -3134,52 +3084,50 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T21" t="n">
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>8.639615480865693</v>
       </c>
       <c r="V21" t="n">
-        <v>8.639615480865693</v>
+        <v>-2.513070406560536</v>
       </c>
       <c r="W21" t="n">
-        <v>-2.513070406560536</v>
+        <v>-4.158033170070452</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.158033170070452</v>
+        <v>10.11782309310898</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.489999999999999</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2274.658663444444</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-32.21412589294149</v>
+      </c>
+      <c r="AB21" t="n">
         <v>10.11782309310898</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.489999999999999</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2274.658663444444</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-32.21412589294149</v>
-      </c>
       <c r="AC21" t="n">
-        <v>10.11782309310898</v>
+        <v>4.857823093108979</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.857823093108979</v>
+        <v>2881008.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>2881008.1</v>
+        <v>32.44234891252128</v>
       </c>
       <c r="AF21" t="n">
-        <v>32.44234891252128</v>
+        <v>42.60152201585271</v>
       </c>
       <c r="AG21" t="n">
-        <v>42.60152201585271</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3188,28 +3136,28 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="n">
         <v>9.09</v>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP21" t="n">
+        <v>7.2</v>
+      </c>
       <c r="AQ21" t="n">
-        <v>7.2</v>
+        <v>7.11</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.11</v>
+        <v>10.91108580725597</v>
       </c>
     </row>
     <row r="22">
@@ -3268,55 +3216,53 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T22" t="n">
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>13.74506711302919</v>
       </c>
       <c r="V22" t="n">
-        <v>13.74506711302919</v>
+        <v>3.546380318699183</v>
       </c>
       <c r="W22" t="n">
-        <v>3.546380318699183</v>
+        <v>0.4082080070155092</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4082080070155092</v>
+        <v>10.29374846651843</v>
       </c>
       <c r="Y22" t="n">
+        <v>0.8444444444444432</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3045.102807444444</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-22.23473686905505</v>
+      </c>
+      <c r="AB22" t="n">
         <v>10.29374846651843</v>
       </c>
-      <c r="Z22" t="n">
-        <v>0.8444444444444432</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3045.102807444444</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-22.23473686905505</v>
-      </c>
       <c r="AC22" t="n">
-        <v>10.29374846651843</v>
+        <v>4.627081799851759</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.627081799851759</v>
+        <v>2851758.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>2851758.2</v>
+        <v>33.4364743827159</v>
       </c>
       <c r="AF22" t="n">
-        <v>33.4364743827159</v>
+        <v>43.15129873212954</v>
       </c>
       <c r="AG22" t="n">
-        <v>43.15129873212954</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
         <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -3327,23 +3273,23 @@
       <c r="AL22" t="n">
         <v>0</v>
       </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="n">
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="n">
         <v>8.68</v>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP22" t="n">
+        <v>9.09</v>
+      </c>
       <c r="AQ22" t="n">
-        <v>9.09</v>
+        <v>7.59</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.59</v>
+        <v>9.008750801642318</v>
       </c>
     </row>
     <row r="23">
@@ -3402,58 +3348,56 @@
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T23" t="n">
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>8.240009143024984</v>
       </c>
       <c r="V23" t="n">
-        <v>8.240009143024984</v>
+        <v>2.457148141955234</v>
       </c>
       <c r="W23" t="n">
-        <v>2.457148141955234</v>
+        <v>-0.1052770982733375</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1052770982733375</v>
+        <v>13.64568713425012</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3065.94998488889</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-6.065190853527803</v>
+      </c>
+      <c r="AB23" t="n">
         <v>13.64568713425012</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3065.94998488889</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-6.065190853527803</v>
-      </c>
       <c r="AC23" t="n">
-        <v>13.64568713425012</v>
+        <v>8.475687134250117</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.475687134250117</v>
+        <v>2870854.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>2870854.4</v>
+        <v>31.83494084548489</v>
       </c>
       <c r="AF23" t="n">
-        <v>31.83494084548489</v>
+        <v>44.15987449589921</v>
       </c>
       <c r="AG23" t="n">
-        <v>44.15987449589921</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3461,23 +3405,23 @@
       <c r="AL23" t="n">
         <v>0</v>
       </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="n">
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="n">
         <v>9.67</v>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP23" t="n">
+        <v>8.68</v>
+      </c>
       <c r="AQ23" t="n">
-        <v>8.68</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.029999999999999</v>
+        <v>12.09976118372467</v>
       </c>
     </row>
     <row r="24">
@@ -3536,82 +3480,80 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T24" t="n">
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6.666855650429726</v>
       </c>
       <c r="V24" t="n">
-        <v>6.666855650429726</v>
+        <v>6.875498179136375</v>
       </c>
       <c r="W24" t="n">
-        <v>6.875498179136375</v>
+        <v>10.61767341467406</v>
       </c>
       <c r="X24" t="n">
-        <v>10.61767341467406</v>
+        <v>6.20367820751595</v>
       </c>
       <c r="Y24" t="n">
+        <v>2.511397849462365</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3316.391325333333</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>15.46164327172481</v>
+      </c>
+      <c r="AB24" t="n">
         <v>6.20367820751595</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.511397849462365</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3316.391325333333</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>15.46164327172481</v>
-      </c>
       <c r="AC24" t="n">
-        <v>6.20367820751595</v>
+        <v>2.457011540849284</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.457011540849284</v>
+        <v>2978751.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2978751.2</v>
+        <v>31.32789338028634</v>
       </c>
       <c r="AF24" t="n">
-        <v>31.32789338028634</v>
+        <v>43.5870071995271</v>
       </c>
       <c r="AG24" t="n">
-        <v>43.5870071995271</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="n">
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="n">
         <v>8.58</v>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP24" t="n">
+        <v>9.67</v>
+      </c>
       <c r="AQ24" t="n">
-        <v>9.67</v>
+        <v>7.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.2</v>
+        <v>4.709945027083573</v>
       </c>
     </row>
     <row r="25">
@@ -3670,52 +3612,50 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T25" t="n">
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>5.591126762085352</v>
       </c>
       <c r="V25" t="n">
-        <v>5.591126762085352</v>
+        <v>7.028176335068204</v>
       </c>
       <c r="W25" t="n">
-        <v>7.028176335068204</v>
+        <v>6.982130576597823</v>
       </c>
       <c r="X25" t="n">
-        <v>6.982130576597823</v>
+        <v>10.10814030226557</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3597.143322666667</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>58.13991701153198</v>
+      </c>
+      <c r="AB25" t="n">
         <v>10.10814030226557</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3597.143322666667</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>58.13991701153198</v>
-      </c>
       <c r="AC25" t="n">
-        <v>10.10814030226557</v>
+        <v>6.538140302265568</v>
       </c>
       <c r="AD25" t="n">
-        <v>6.538140302265568</v>
+        <v>3054867.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>3054867.5</v>
+        <v>32.3066417774257</v>
       </c>
       <c r="AF25" t="n">
-        <v>32.3066417774257</v>
+        <v>42.99140633759075</v>
       </c>
       <c r="AG25" t="n">
-        <v>42.99140633759075</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3724,28 +3664,28 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="n">
         <v>6.29</v>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP25" t="n">
+        <v>8.58</v>
+      </c>
       <c r="AQ25" t="n">
-        <v>8.58</v>
+        <v>9.09</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.09</v>
+        <v>8.163896591586761</v>
       </c>
     </row>
     <row r="26">
@@ -3804,55 +3744,53 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T26" t="n">
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.067751173170262</v>
       </c>
       <c r="V26" t="n">
-        <v>1.067751173170262</v>
+        <v>3.948631594026897</v>
       </c>
       <c r="W26" t="n">
-        <v>3.948631594026897</v>
+        <v>21.73477881766106</v>
       </c>
       <c r="X26" t="n">
-        <v>21.73477881766106</v>
+        <v>6.997780141657595</v>
       </c>
       <c r="Y26" t="n">
+        <v>4.039999999999999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3201.643760999999</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.140744449509405</v>
+      </c>
+      <c r="AB26" t="n">
         <v>6.997780141657595</v>
       </c>
-      <c r="Z26" t="n">
-        <v>4.039999999999999</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3201.643760999999</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>5.140744449509405</v>
-      </c>
       <c r="AC26" t="n">
-        <v>6.997780141657595</v>
+        <v>4.787780141657594</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.787780141657594</v>
+        <v>2953345.399999999</v>
       </c>
       <c r="AE26" t="n">
-        <v>2953345.399999999</v>
+        <v>32.63108676689154</v>
       </c>
       <c r="AF26" t="n">
-        <v>32.63108676689154</v>
+        <v>47.09104123073449</v>
       </c>
       <c r="AG26" t="n">
-        <v>47.09104123073449</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
         <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -3863,23 +3801,23 @@
       <c r="AL26" t="n">
         <v>0</v>
       </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="n">
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="n">
         <v>6.11</v>
       </c>
-      <c r="AP26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP26" t="n">
+        <v>6.29</v>
+      </c>
       <c r="AQ26" t="n">
-        <v>6.29</v>
+        <v>8.68</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.68</v>
+        <v>5.640994972621405</v>
       </c>
     </row>
     <row r="27">
@@ -3938,58 +3876,56 @@
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T27" t="n">
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>6.412776928945041</v>
       </c>
       <c r="V27" t="n">
-        <v>6.412776928945041</v>
+        <v>4.654156833996614</v>
       </c>
       <c r="W27" t="n">
-        <v>4.654156833996614</v>
+        <v>10.56970803731674</v>
       </c>
       <c r="X27" t="n">
-        <v>10.56970803731674</v>
+        <v>5.559141706560822</v>
       </c>
       <c r="Y27" t="n">
+        <v>3.112688172043011</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3350.068524</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9.266900651068743</v>
+      </c>
+      <c r="AB27" t="n">
         <v>5.559141706560822</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.112688172043011</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3350.068524</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9.266900651068743</v>
-      </c>
       <c r="AC27" t="n">
-        <v>5.559141706560822</v>
+        <v>2.585808373227489</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.585808373227489</v>
+        <v>2994242.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2994242.5</v>
+        <v>32.4804487278502</v>
       </c>
       <c r="AF27" t="n">
-        <v>32.4804487278502</v>
+        <v>45.60718779457575</v>
       </c>
       <c r="AG27" t="n">
-        <v>45.60718779457575</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -3997,23 +3933,23 @@
       <c r="AL27" t="n">
         <v>0</v>
       </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="n">
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="n">
         <v>5.32</v>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP27" t="n">
+        <v>6.11</v>
+      </c>
       <c r="AQ27" t="n">
-        <v>6.11</v>
+        <v>9.67</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.67</v>
+        <v>6.518715167421196</v>
       </c>
     </row>
     <row r="28">
@@ -4072,82 +4008,80 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T28" t="n">
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>9.265500760839295</v>
       </c>
       <c r="V28" t="n">
-        <v>9.265500760839295</v>
+        <v>4.50683307705424</v>
       </c>
       <c r="W28" t="n">
-        <v>4.50683307705424</v>
+        <v>14.09341674061191</v>
       </c>
       <c r="X28" t="n">
-        <v>14.09341674061191</v>
+        <v>10.01935732644641</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.443333333333333</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3982.758961999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>20.0931546158742</v>
+      </c>
+      <c r="AB28" t="n">
         <v>10.01935732644641</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.443333333333333</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3982.758961999999</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>20.0931546158742</v>
-      </c>
       <c r="AC28" t="n">
-        <v>10.01935732644641</v>
+        <v>5.462690659779744</v>
       </c>
       <c r="AD28" t="n">
-        <v>5.462690659779744</v>
+        <v>3103022.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>3103022.7</v>
+        <v>32.85969516110855</v>
       </c>
       <c r="AF28" t="n">
-        <v>32.85969516110855</v>
+        <v>45.82658064344808</v>
       </c>
       <c r="AG28" t="n">
-        <v>45.82658064344808</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
       </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="n">
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="n">
         <v>6.67</v>
       </c>
-      <c r="AP28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP28" t="n">
+        <v>5.32</v>
+      </c>
       <c r="AQ28" t="n">
-        <v>5.32</v>
+        <v>8.58</v>
       </c>
       <c r="AR28" t="n">
-        <v>8.58</v>
+        <v>10.26152247813552</v>
       </c>
     </row>
     <row r="29">
@@ -4206,52 +4140,50 @@
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T29" t="n">
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>14.21162558333961</v>
       </c>
       <c r="V29" t="n">
-        <v>14.21162558333961</v>
+        <v>5.103139136687784</v>
       </c>
       <c r="W29" t="n">
-        <v>5.103139136687784</v>
+        <v>23.56981900730852</v>
       </c>
       <c r="X29" t="n">
-        <v>23.56981900730852</v>
+        <v>9.151438935891075</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.403333333333333</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4298.677193555555</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>19.5025276437643</v>
+      </c>
+      <c r="AB29" t="n">
         <v>9.151438935891075</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.403333333333333</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4298.677193555555</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>19.5025276437643</v>
-      </c>
       <c r="AC29" t="n">
-        <v>9.151438935891075</v>
+        <v>4.554772269224409</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.554772269224409</v>
+        <v>3231777.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>3231777.6</v>
+        <v>34.87811785068378</v>
       </c>
       <c r="AF29" t="n">
-        <v>34.87811785068378</v>
+        <v>46.47366204902218</v>
       </c>
       <c r="AG29" t="n">
-        <v>46.47366204902218</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4260,28 +4192,28 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="n">
         <v>8.93</v>
       </c>
-      <c r="AP29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP29" t="n">
+        <v>6.67</v>
+      </c>
       <c r="AQ29" t="n">
-        <v>6.67</v>
+        <v>6.29</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.29</v>
+        <v>9.997605700656621</v>
       </c>
     </row>
     <row r="30">
@@ -4340,55 +4272,53 @@
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T30" t="n">
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>14.36150778757108</v>
       </c>
       <c r="V30" t="n">
-        <v>14.36150778757108</v>
+        <v>9.135222967313727</v>
       </c>
       <c r="W30" t="n">
-        <v>9.135222967313727</v>
+        <v>5.259283367834988</v>
       </c>
       <c r="X30" t="n">
-        <v>5.259283367834988</v>
+        <v>9.756405440982574</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.279444444444444</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4990.7252</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>55.88009074567371</v>
+      </c>
+      <c r="AB30" t="n">
         <v>9.756405440982574</v>
       </c>
-      <c r="Z30" t="n">
-        <v>1.279444444444444</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4990.7252</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>55.88009074567371</v>
-      </c>
       <c r="AC30" t="n">
-        <v>9.756405440982574</v>
+        <v>4.966405440982574</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.966405440982574</v>
+        <v>3244054.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>3244054.3</v>
+        <v>33.97328460254194</v>
       </c>
       <c r="AF30" t="n">
-        <v>33.97328460254194</v>
+        <v>45.87483939464268</v>
       </c>
       <c r="AG30" t="n">
-        <v>45.87483939464268</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
         <v>1</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
@@ -4399,23 +4329,23 @@
       <c r="AL30" t="n">
         <v>0</v>
       </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="n">
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="n">
         <v>7.5</v>
       </c>
-      <c r="AP30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP30" t="n">
+        <v>8.93</v>
+      </c>
       <c r="AQ30" t="n">
-        <v>8.93</v>
+        <v>6.11</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.11</v>
+        <v>12.81782525137924</v>
       </c>
     </row>
     <row r="31">
@@ -4474,58 +4404,56 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T31" t="n">
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>12.86741547986445</v>
       </c>
       <c r="V31" t="n">
-        <v>12.86741547986445</v>
+        <v>12.13194484375899</v>
       </c>
       <c r="W31" t="n">
-        <v>12.13194484375899</v>
+        <v>18.09671167835027</v>
       </c>
       <c r="X31" t="n">
-        <v>18.09671167835027</v>
+        <v>9.394318688626569</v>
       </c>
       <c r="Y31" t="n">
+        <v>2.563333333333333</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5277.047220444445</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>57.52057555358962</v>
+      </c>
+      <c r="AB31" t="n">
         <v>9.394318688626569</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.563333333333333</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5277.047220444445</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>57.52057555358962</v>
-      </c>
       <c r="AC31" t="n">
-        <v>9.394318688626569</v>
+        <v>5.540985355293236</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.540985355293236</v>
+        <v>3244734.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>3244734.5</v>
+        <v>33.82972012039814</v>
       </c>
       <c r="AF31" t="n">
-        <v>33.82972012039814</v>
+        <v>48.52609666522793</v>
       </c>
       <c r="AG31" t="n">
-        <v>48.52609666522793</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4533,23 +4461,23 @@
       <c r="AL31" t="n">
         <v>0</v>
       </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="n">
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="n">
         <v>6.46</v>
       </c>
-      <c r="AP31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP31" t="n">
+        <v>7.5</v>
+      </c>
       <c r="AQ31" t="n">
-        <v>7.5</v>
+        <v>5.32</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.32</v>
+        <v>12.50371788427496</v>
       </c>
     </row>
     <row r="32">
@@ -4608,82 +4536,80 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T32" t="n">
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>12.84924205884448</v>
       </c>
       <c r="V32" t="n">
-        <v>12.84924205884448</v>
+        <v>15.17864957504445</v>
       </c>
       <c r="W32" t="n">
-        <v>15.17864957504445</v>
+        <v>12.10749283724164</v>
       </c>
       <c r="X32" t="n">
-        <v>12.10749283724164</v>
+        <v>10.15251467325937</v>
       </c>
       <c r="Y32" t="n">
+        <v>3.893333333333333</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4880.271473777778</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>22.53494425198856</v>
+      </c>
+      <c r="AB32" t="n">
         <v>10.15251467325937</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.893333333333333</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4880.271473777778</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>22.53494425198856</v>
-      </c>
       <c r="AC32" t="n">
-        <v>10.15251467325937</v>
+        <v>7.545848006592704</v>
       </c>
       <c r="AD32" t="n">
-        <v>7.545848006592704</v>
+        <v>3390979.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>3390979.6</v>
+        <v>33.93297618186792</v>
       </c>
       <c r="AF32" t="n">
-        <v>33.93297618186792</v>
+        <v>47.59802742546727</v>
       </c>
       <c r="AG32" t="n">
-        <v>47.59802742546727</v>
+        <v>3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
       </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="n">
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="n">
         <v>6.23</v>
       </c>
-      <c r="AP32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP32" t="n">
+        <v>6.46</v>
+      </c>
       <c r="AQ32" t="n">
-        <v>6.46</v>
+        <v>6.67</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.67</v>
+        <v>15.11314187668522</v>
       </c>
     </row>
     <row r="33">
@@ -4742,52 +4668,50 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T33" t="n">
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>5.57755828866151</v>
       </c>
       <c r="V33" t="n">
-        <v>5.57755828866151</v>
+        <v>11.24284224318506</v>
       </c>
       <c r="W33" t="n">
-        <v>11.24284224318506</v>
+        <v>0.7659880365536331</v>
       </c>
       <c r="X33" t="n">
-        <v>0.7659880365536331</v>
+        <v>10.52441362486438</v>
       </c>
       <c r="Y33" t="n">
+        <v>3.884523809523811</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4452.080520333333</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.56861703892899</v>
+      </c>
+      <c r="AB33" t="n">
         <v>10.52441362486438</v>
       </c>
-      <c r="Z33" t="n">
-        <v>3.884523809523811</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4452.080520333333</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>3.56861703892899</v>
-      </c>
       <c r="AC33" t="n">
-        <v>10.52441362486438</v>
+        <v>8.057746958197715</v>
       </c>
       <c r="AD33" t="n">
-        <v>8.057746958197715</v>
+        <v>3508749.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>3508749.9</v>
+        <v>33.91670919605868</v>
       </c>
       <c r="AF33" t="n">
-        <v>33.91670919605868</v>
+        <v>45.1885755664717</v>
       </c>
       <c r="AG33" t="n">
-        <v>45.1885755664717</v>
+        <v>4</v>
       </c>
       <c r="AH33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4796,28 +4720,28 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="n">
         <v>5.72</v>
       </c>
-      <c r="AP33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP33" t="n">
+        <v>6.23</v>
+      </c>
       <c r="AQ33" t="n">
-        <v>6.23</v>
+        <v>8.93</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.93</v>
+        <v>13.2897521039921</v>
       </c>
     </row>
     <row r="34">
@@ -4876,55 +4800,53 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T34" t="n">
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>8.190248938447064</v>
       </c>
       <c r="V34" t="n">
-        <v>8.190248938447064</v>
+        <v>2.779081806547867</v>
       </c>
       <c r="W34" t="n">
-        <v>2.779081806547867</v>
+        <v>9.191675674747879</v>
       </c>
       <c r="X34" t="n">
-        <v>9.191675674747879</v>
+        <v>10.08965558363613</v>
       </c>
       <c r="Y34" t="n">
+        <v>2.865555555555555</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4793.374304222222</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-3.954353082349182</v>
+      </c>
+      <c r="AB34" t="n">
         <v>10.08965558363613</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.865555555555555</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4793.374304222222</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-3.954353082349182</v>
-      </c>
       <c r="AC34" t="n">
-        <v>10.08965558363613</v>
+        <v>7.016322250302792</v>
       </c>
       <c r="AD34" t="n">
-        <v>7.016322250302792</v>
+        <v>3406426.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>3406426.6</v>
+        <v>35.00376318104139</v>
       </c>
       <c r="AF34" t="n">
-        <v>35.00376318104139</v>
+        <v>46.41580711000788</v>
       </c>
       <c r="AG34" t="n">
-        <v>46.41580711000788</v>
+        <v>1</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -4935,23 +4857,23 @@
       <c r="AL34" t="n">
         <v>0</v>
       </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="n">
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="n">
         <v>5.1</v>
       </c>
-      <c r="AP34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP34" t="n">
+        <v>5.72</v>
+      </c>
       <c r="AQ34" t="n">
-        <v>5.72</v>
+        <v>7.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.5</v>
+        <v>12.00719132972217</v>
       </c>
     </row>
     <row r="35">
@@ -5010,58 +4932,56 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T35" t="n">
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>-0.78610923392749</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.78610923392749</v>
+        <v>-1.740511069588535</v>
       </c>
       <c r="W35" t="n">
-        <v>-1.740511069588535</v>
+        <v>-2.213207452270327</v>
       </c>
       <c r="X35" t="n">
-        <v>-2.213207452270327</v>
+        <v>9.646179163555789</v>
       </c>
       <c r="Y35" t="n">
+        <v>2.065913978494624</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4361.682420333333</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-17.34615518627135</v>
+      </c>
+      <c r="AB35" t="n">
         <v>9.646179163555789</v>
       </c>
-      <c r="Z35" t="n">
-        <v>2.065913978494624</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>4361.682420333333</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-17.34615518627135</v>
-      </c>
       <c r="AC35" t="n">
-        <v>9.646179163555789</v>
+        <v>6.172845830222457</v>
       </c>
       <c r="AD35" t="n">
-        <v>6.172845830222457</v>
+        <v>3381041.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>3381041.2</v>
+        <v>32.21065747438984</v>
       </c>
       <c r="AF35" t="n">
-        <v>32.21065747438984</v>
+        <v>45.63941131507063</v>
       </c>
       <c r="AG35" t="n">
-        <v>45.63941131507063</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5069,23 +4989,23 @@
       <c r="AL35" t="n">
         <v>0</v>
       </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="n">
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="n">
         <v>4.3</v>
       </c>
-      <c r="AP35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP35" t="n">
+        <v>5.1</v>
+      </c>
       <c r="AQ35" t="n">
-        <v>5.1</v>
+        <v>6.46</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.46</v>
+        <v>8.764409462889567</v>
       </c>
     </row>
     <row r="36">
@@ -5144,82 +5064,80 @@
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T36" t="n">
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>-1.72817294556874</v>
       </c>
       <c r="V36" t="n">
-        <v>-1.72817294556874</v>
+        <v>-5.089827755510401</v>
       </c>
       <c r="W36" t="n">
-        <v>-5.089827755510401</v>
+        <v>-7.087678502646333</v>
       </c>
       <c r="X36" t="n">
-        <v>-7.087678502646333</v>
+        <v>10.40079043222437</v>
       </c>
       <c r="Y36" t="n">
+        <v>-0.6786021505376327</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4516.561138999999</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-7.452666039830635</v>
+      </c>
+      <c r="AB36" t="n">
         <v>10.40079043222437</v>
       </c>
-      <c r="Z36" t="n">
-        <v>-0.6786021505376327</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4516.561138999999</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-7.452666039830635</v>
-      </c>
       <c r="AC36" t="n">
-        <v>10.40079043222437</v>
+        <v>4.564123765557706</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.564123765557706</v>
+        <v>3532631.6</v>
       </c>
       <c r="AE36" t="n">
-        <v>3532631.6</v>
+        <v>32.00942039922872</v>
       </c>
       <c r="AF36" t="n">
-        <v>32.00942039922872</v>
+        <v>42.87235045964034</v>
       </c>
       <c r="AG36" t="n">
-        <v>42.87235045964034</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="n">
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="n">
         <v>3.26</v>
       </c>
-      <c r="AP36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP36" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AQ36" t="n">
-        <v>4.3</v>
+        <v>6.23</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.23</v>
+        <v>7.104158352677037</v>
       </c>
     </row>
     <row r="37">
@@ -5278,52 +5196,50 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T37" t="n">
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>-0.8135439402883526</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.8135439402883526</v>
+        <v>-8.775033745258142</v>
       </c>
       <c r="W37" t="n">
-        <v>-8.775033745258142</v>
+        <v>-2.614661574337707</v>
       </c>
       <c r="X37" t="n">
-        <v>-2.614661574337707</v>
+        <v>8.863988283975676</v>
       </c>
       <c r="Y37" t="n">
+        <v>-1.56032258064516</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3651.065773333334</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-17.99191958325197</v>
+      </c>
+      <c r="AB37" t="n">
         <v>8.863988283975676</v>
       </c>
-      <c r="Z37" t="n">
-        <v>-1.56032258064516</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3651.065773333334</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>-17.99191958325197</v>
-      </c>
       <c r="AC37" t="n">
-        <v>8.863988283975676</v>
+        <v>2.193988283975677</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.193988283975677</v>
+        <v>3512440.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>3512440.2</v>
+        <v>33.60543761001255</v>
       </c>
       <c r="AF37" t="n">
-        <v>33.60543761001255</v>
+        <v>42.6176764518297</v>
       </c>
       <c r="AG37" t="n">
-        <v>42.6176764518297</v>
+        <v>4</v>
       </c>
       <c r="AH37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5332,28 +5248,28 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="n">
         <v>2.94</v>
       </c>
-      <c r="AP37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP37" t="n">
+        <v>3.26</v>
+      </c>
       <c r="AQ37" t="n">
-        <v>3.26</v>
+        <v>5.72</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.72</v>
+        <v>6.131347384614783</v>
       </c>
     </row>
     <row r="38">
@@ -5412,55 +5328,53 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>-42.36494734259914</v>
       </c>
       <c r="V38" t="n">
-        <v>-42.36494734259914</v>
+        <v>-23.71262721854784</v>
       </c>
       <c r="W38" t="n">
-        <v>-23.71262721854784</v>
+        <v>-40.29777148094308</v>
       </c>
       <c r="X38" t="n">
-        <v>-40.29777148094308</v>
+        <v>12.31920706109511</v>
       </c>
       <c r="Y38" t="n">
+        <v>-2.349677419354839</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2226.407810666667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-53.55238983307551</v>
+      </c>
+      <c r="AB38" t="n">
         <v>12.31920706109511</v>
       </c>
-      <c r="Z38" t="n">
-        <v>-2.349677419354839</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2226.407810666667</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-53.55238983307551</v>
-      </c>
       <c r="AC38" t="n">
-        <v>12.31920706109511</v>
+        <v>5.745873727761773</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.745873727761773</v>
+        <v>2661511.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>2661511.5</v>
+        <v>25.82094422661709</v>
       </c>
       <c r="AF38" t="n">
-        <v>25.82094422661709</v>
+        <v>39.84931119027665</v>
       </c>
       <c r="AG38" t="n">
-        <v>39.84931119027665</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
         <v>1</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -5469,25 +5383,25 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AP38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP38" t="n">
+        <v>2.94</v>
+      </c>
       <c r="AQ38" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.1</v>
+        <v>6.186377293058576</v>
       </c>
     </row>
     <row r="39">
@@ -5546,82 +5460,80 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T39" t="n">
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>-2.228995470938311</v>
       </c>
       <c r="V39" t="n">
-        <v>-2.228995470938311</v>
+        <v>-3.988524797773596</v>
       </c>
       <c r="W39" t="n">
-        <v>-3.988524797773596</v>
+        <v>-16.64516974413968</v>
       </c>
       <c r="X39" t="n">
-        <v>-16.64516974413968</v>
+        <v>12.17640495793575</v>
       </c>
       <c r="Y39" t="n">
+        <v>-2.896666666666667</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3195.712981111111</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-26.73210304782151</v>
+      </c>
+      <c r="AB39" t="n">
         <v>12.17640495793575</v>
       </c>
-      <c r="Z39" t="n">
-        <v>-2.896666666666667</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3195.712981111111</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-26.73210304782151</v>
-      </c>
       <c r="AC39" t="n">
-        <v>12.17640495793575</v>
+        <v>5.279738291269081</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.279738291269081</v>
+        <v>3209692.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>3209692.4</v>
+        <v>33.17391411089736</v>
       </c>
       <c r="AF39" t="n">
-        <v>33.17391411089736</v>
+        <v>42.85409405586654</v>
       </c>
       <c r="AG39" t="n">
-        <v>42.85409405586654</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="n">
         <v>-5.84</v>
       </c>
-      <c r="AP39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP39" t="n">
+        <v>-23.13</v>
+      </c>
       <c r="AQ39" t="n">
-        <v>-23.13</v>
+        <v>4.3</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.3</v>
+        <v>5.146224512525066</v>
       </c>
     </row>
     <row r="40">
@@ -5680,82 +5592,80 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T40" t="n">
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.208697946868134</v>
       </c>
       <c r="V40" t="n">
-        <v>4.208697946868134</v>
+        <v>-6.42719595567115</v>
       </c>
       <c r="W40" t="n">
-        <v>-6.42719595567115</v>
+        <v>-3.993652770907252</v>
       </c>
       <c r="X40" t="n">
-        <v>-3.993652770907252</v>
+        <v>12.40363992150963</v>
       </c>
       <c r="Y40" t="n">
+        <v>-2.376666666666666</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3266.704911666666</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-27.67274014163042</v>
+      </c>
+      <c r="AB40" t="n">
         <v>12.40363992150963</v>
       </c>
-      <c r="Z40" t="n">
-        <v>-2.376666666666666</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3266.704911666666</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>-27.67274014163042</v>
-      </c>
       <c r="AC40" t="n">
-        <v>12.40363992150963</v>
+        <v>6.026973254842969</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.026973254842969</v>
+        <v>3583773.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>3583773.5</v>
+        <v>32.88058801707195</v>
       </c>
       <c r="AF40" t="n">
-        <v>32.88058801707195</v>
+        <v>40.09277092985927</v>
       </c>
       <c r="AG40" t="n">
-        <v>40.09277092985927</v>
+        <v>3</v>
       </c>
       <c r="AH40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="n">
         <v>1.78</v>
       </c>
-      <c r="AP40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP40" t="n">
+        <v>-5.84</v>
+      </c>
       <c r="AQ40" t="n">
-        <v>-5.84</v>
+        <v>3.26</v>
       </c>
       <c r="AR40" t="n">
-        <v>3.26</v>
+        <v>6.027607325443429</v>
       </c>
     </row>
     <row r="41">
@@ -5814,52 +5724,50 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T41" t="n">
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>13.2110593373659</v>
       </c>
       <c r="V41" t="n">
-        <v>13.2110593373659</v>
+        <v>6.379887179004173</v>
       </c>
       <c r="W41" t="n">
-        <v>6.379887179004173</v>
+        <v>13.30458006689888</v>
       </c>
       <c r="X41" t="n">
-        <v>13.30458006689888</v>
+        <v>12.17034968442652</v>
       </c>
       <c r="Y41" t="n">
+        <v>-0.8700000000000001</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4432.940711333334</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>21.41497816091567</v>
+      </c>
+      <c r="AB41" t="n">
         <v>12.17034968442652</v>
       </c>
-      <c r="Z41" t="n">
-        <v>-0.8700000000000001</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4432.940711333334</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>21.41497816091567</v>
-      </c>
       <c r="AC41" t="n">
-        <v>12.17034968442652</v>
+        <v>7.300349684426519</v>
       </c>
       <c r="AD41" t="n">
-        <v>7.300349684426519</v>
+        <v>3827029.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>3827029.2</v>
+        <v>34.91769542808819</v>
       </c>
       <c r="AF41" t="n">
-        <v>34.91769542808819</v>
+        <v>43.05435401433571</v>
       </c>
       <c r="AG41" t="n">
-        <v>43.05435401433571</v>
+        <v>4</v>
       </c>
       <c r="AH41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5868,28 +5776,28 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL41" t="n">
         <v>1</v>
       </c>
-      <c r="AM41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="n">
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="n">
         <v>3.29</v>
       </c>
-      <c r="AP41" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP41" t="n">
+        <v>1.78</v>
+      </c>
       <c r="AQ41" t="n">
-        <v>1.78</v>
+        <v>2.94</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.94</v>
+        <v>5.579559218087171</v>
       </c>
     </row>
     <row r="42">
@@ -5948,55 +5856,53 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T42" t="n">
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>66.5234535177148</v>
       </c>
       <c r="V42" t="n">
-        <v>66.5234535177148</v>
+        <v>46.47504144241408</v>
       </c>
       <c r="W42" t="n">
-        <v>46.47504144241408</v>
+        <v>45.13112955321681</v>
       </c>
       <c r="X42" t="n">
-        <v>45.13112955321681</v>
+        <v>10.70917123775022</v>
       </c>
       <c r="Y42" t="n">
+        <v>-1.596666666666667</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5077.564255555556</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>128.0608355409583</v>
+      </c>
+      <c r="AB42" t="n">
         <v>10.70917123775022</v>
       </c>
-      <c r="Z42" t="n">
-        <v>-1.596666666666667</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>5077.564255555556</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>128.0608355409583</v>
-      </c>
       <c r="AC42" t="n">
-        <v>10.70917123775022</v>
+        <v>5.112504571083549</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.112504571083549</v>
+        <v>3377295.100000001</v>
       </c>
       <c r="AE42" t="n">
-        <v>3377295.100000001</v>
+        <v>33.88495130318934</v>
       </c>
       <c r="AF42" t="n">
-        <v>33.88495130318934</v>
+        <v>45.78994888542609</v>
       </c>
       <c r="AG42" t="n">
-        <v>45.78994888542609</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
         <v>1</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
         <v>0</v>
@@ -6007,23 +5913,23 @@
       <c r="AL42" t="n">
         <v>0</v>
       </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="n">
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="n">
         <v>22.63</v>
       </c>
-      <c r="AP42" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP42" t="n">
+        <v>3.29</v>
+      </c>
       <c r="AQ42" t="n">
-        <v>3.29</v>
+        <v>-23.13</v>
       </c>
       <c r="AR42" t="n">
-        <v>-23.13</v>
+        <v>5.818790729730394</v>
       </c>
     </row>
     <row r="43">
@@ -6082,58 +5988,56 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T43" t="n">
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>15.299198726949</v>
       </c>
       <c r="V43" t="n">
-        <v>15.299198726949</v>
+        <v>25.39220425950273</v>
       </c>
       <c r="W43" t="n">
-        <v>25.39220425950273</v>
+        <v>26.84168984466506</v>
       </c>
       <c r="X43" t="n">
-        <v>26.84168984466506</v>
+        <v>9.337915541986884</v>
       </c>
       <c r="Y43" t="n">
+        <v>-1.079999999999999</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>5443.51475</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>70.33803668148433</v>
+      </c>
+      <c r="AB43" t="n">
         <v>9.337915541986884</v>
       </c>
-      <c r="Z43" t="n">
-        <v>-1.079999999999999</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5443.51475</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>70.33803668148433</v>
-      </c>
       <c r="AC43" t="n">
-        <v>9.337915541986884</v>
+        <v>4.257915541986885</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.257915541986885</v>
+        <v>3625478.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>3625478.1</v>
+        <v>33.86266489928597</v>
       </c>
       <c r="AF43" t="n">
-        <v>33.86266489928597</v>
+        <v>47.85230119028991</v>
       </c>
       <c r="AG43" t="n">
-        <v>47.85230119028991</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -6141,23 +6045,23 @@
       <c r="AL43" t="n">
         <v>0</v>
       </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="n">
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="AP43" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP43" t="n">
+        <v>22.63</v>
+      </c>
       <c r="AQ43" t="n">
-        <v>22.63</v>
+        <v>-5.84</v>
       </c>
       <c r="AR43" t="n">
-        <v>-5.84</v>
+        <v>6.671182051341229</v>
       </c>
     </row>
     <row r="44">
@@ -6216,82 +6120,80 @@
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T44" t="n">
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.596743897353449</v>
       </c>
       <c r="V44" t="n">
-        <v>3.596743897353449</v>
+        <v>28.13969126073221</v>
       </c>
       <c r="W44" t="n">
-        <v>28.13969126073221</v>
+        <v>19.99142574024248</v>
       </c>
       <c r="X44" t="n">
-        <v>19.99142574024248</v>
+        <v>11.40194927174409</v>
       </c>
       <c r="Y44" t="n">
+        <v>-1.016666666666667</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>5963.277718666666</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>82.5471807193082</v>
+      </c>
+      <c r="AB44" t="n">
         <v>11.40194927174409</v>
       </c>
-      <c r="Z44" t="n">
-        <v>-1.016666666666667</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>5963.277718666666</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>82.5471807193082</v>
-      </c>
       <c r="AC44" t="n">
-        <v>11.40194927174409</v>
+        <v>6.385282605077427</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.385282605077427</v>
+        <v>3896581.3</v>
       </c>
       <c r="AE44" t="n">
-        <v>3896581.3</v>
+        <v>31.32870857846595</v>
       </c>
       <c r="AF44" t="n">
-        <v>31.32870857846595</v>
+        <v>45.62916985717711</v>
       </c>
       <c r="AG44" t="n">
-        <v>45.62916985717711</v>
+        <v>3</v>
       </c>
       <c r="AH44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
       </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="n">
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="n">
         <v>5.53</v>
       </c>
-      <c r="AP44" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP44" t="n">
+        <v>9.869999999999999</v>
+      </c>
       <c r="AQ44" t="n">
-        <v>9.869999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.78</v>
+        <v>9.813660365087728</v>
       </c>
     </row>
     <row r="45">
@@ -6350,52 +6252,50 @@
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T45" t="n">
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.370211591558372</v>
       </c>
       <c r="V45" t="n">
-        <v>6.370211591558372</v>
+        <v>22.5491693350361</v>
       </c>
       <c r="W45" t="n">
-        <v>22.5491693350361</v>
+        <v>6.882582051715769</v>
       </c>
       <c r="X45" t="n">
-        <v>6.882582051715769</v>
+        <v>8.751331328013734</v>
       </c>
       <c r="Y45" t="n">
+        <v>-2.343333333333334</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>7545.291487555555</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>70.20961882628231</v>
+      </c>
+      <c r="AB45" t="n">
         <v>8.751331328013734</v>
       </c>
-      <c r="Z45" t="n">
-        <v>-2.343333333333334</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>7545.291487555555</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>70.20961882628231</v>
-      </c>
       <c r="AC45" t="n">
-        <v>8.751331328013734</v>
+        <v>2.4079979946804</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.4079979946804</v>
+        <v>4177237.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>4177237.5</v>
+        <v>34.02813941031603</v>
       </c>
       <c r="AF45" t="n">
-        <v>34.02813941031603</v>
+        <v>44.94689133667885</v>
       </c>
       <c r="AG45" t="n">
-        <v>44.94689133667885</v>
+        <v>4</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6404,28 +6304,28 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="n">
         <v>4.45</v>
       </c>
-      <c r="AP45" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP45" t="n">
+        <v>5.53</v>
+      </c>
       <c r="AQ45" t="n">
-        <v>5.53</v>
+        <v>3.29</v>
       </c>
       <c r="AR45" t="n">
-        <v>3.29</v>
+        <v>8.601347091664913</v>
       </c>
     </row>
     <row r="46">
@@ -6486,55 +6386,53 @@
         <v>6159720.427422995</v>
       </c>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T46" t="n">
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>16.00151451229943</v>
       </c>
       <c r="V46" t="n">
-        <v>16.00151451229943</v>
+        <v>15.75395331097709</v>
       </c>
       <c r="W46" t="n">
-        <v>15.75395331097709</v>
+        <v>24.06931511783677</v>
       </c>
       <c r="X46" t="n">
-        <v>24.06931511783677</v>
+        <v>7.794917877998508</v>
       </c>
       <c r="Y46" t="n">
+        <v>-2.898458781362008</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>8764.095763444446</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>72.60432999651979</v>
+      </c>
+      <c r="AB46" t="n">
         <v>7.794917877998508</v>
       </c>
-      <c r="Z46" t="n">
-        <v>-2.898458781362008</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>8764.095763444446</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>72.60432999651979</v>
-      </c>
       <c r="AC46" t="n">
-        <v>7.794917877998508</v>
+        <v>0.5149178779985082</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.5149178779985082</v>
+        <v>3873955.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>3873955.5</v>
+        <v>34.26769615706738</v>
       </c>
       <c r="AF46" t="n">
-        <v>34.26769615706738</v>
+        <v>47.84110452481966</v>
       </c>
       <c r="AG46" t="n">
-        <v>47.84110452481966</v>
+        <v>1</v>
       </c>
       <c r="AH46" t="n">
         <v>1</v>
       </c>
       <c r="AI46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
         <v>0</v>
@@ -6545,23 +6443,23 @@
       <c r="AL46" t="n">
         <v>0</v>
       </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="n">
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="n">
         <v>13.49</v>
       </c>
-      <c r="AP46" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP46" t="n">
+        <v>4.45</v>
+      </c>
       <c r="AQ46" t="n">
-        <v>4.45</v>
+        <v>22.63</v>
       </c>
       <c r="AR46" t="n">
-        <v>22.63</v>
+        <v>12.06898414518238</v>
       </c>
     </row>
     <row r="47">
@@ -6622,58 +6520,56 @@
         <v>6061356.994818534</v>
       </c>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T47" t="n">
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>6.430973455292022</v>
       </c>
       <c r="V47" t="n">
-        <v>6.430973455292022</v>
+        <v>8.390088652442573</v>
       </c>
       <c r="W47" t="n">
-        <v>8.390088652442573</v>
+        <v>14.00942578430813</v>
       </c>
       <c r="X47" t="n">
-        <v>14.00942578430813</v>
+        <v>8.643959541327151</v>
       </c>
       <c r="Y47" t="n">
+        <v>-1.822616487455197</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>8036.527860888889</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>47.63490557068646</v>
+      </c>
+      <c r="AB47" t="n">
         <v>8.643959541327151</v>
       </c>
-      <c r="Z47" t="n">
-        <v>-1.822616487455197</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>8036.527860888889</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>47.63490557068646</v>
-      </c>
       <c r="AC47" t="n">
-        <v>8.643959541327151</v>
+        <v>1.603959541327151</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.603959541327151</v>
+        <v>3837514.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>3837514.2</v>
+        <v>34.04900755806975</v>
       </c>
       <c r="AF47" t="n">
-        <v>34.04900755806975</v>
+        <v>50.2986256050857</v>
       </c>
       <c r="AG47" t="n">
-        <v>50.2986256050857</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -6681,23 +6577,23 @@
       <c r="AL47" t="n">
         <v>0</v>
       </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="n">
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="n">
         <v>5.96</v>
       </c>
-      <c r="AP47" t="inlineStr">
+      <c r="AO47" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP47" t="n">
+        <v>13.49</v>
+      </c>
       <c r="AQ47" t="n">
-        <v>13.49</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>9.869999999999999</v>
+        <v>15.26956166407503</v>
       </c>
     </row>
     <row r="48">
@@ -6758,82 +6654,80 @@
         <v>6819597.105406575</v>
       </c>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T48" t="n">
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>6.728387810561487</v>
       </c>
       <c r="V48" t="n">
-        <v>6.728387810561487</v>
+        <v>8.205039572031003</v>
       </c>
       <c r="W48" t="n">
-        <v>8.205039572031003</v>
+        <v>2.88041161451511</v>
       </c>
       <c r="X48" t="n">
-        <v>2.88041161451511</v>
+        <v>8.676519473763666</v>
       </c>
       <c r="Y48" t="n">
+        <v>-0.1292473118279549</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>7279.794879555556</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>22.07707276097231</v>
+      </c>
+      <c r="AB48" t="n">
         <v>8.676519473763666</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-0.1292473118279549</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>7279.794879555556</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>22.07707276097231</v>
-      </c>
       <c r="AC48" t="n">
-        <v>8.676519473763666</v>
+        <v>2.553186140430333</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.553186140430333</v>
+        <v>4088046.399999999</v>
       </c>
       <c r="AE48" t="n">
-        <v>4088046.399999999</v>
+        <v>31.87060939425737</v>
       </c>
       <c r="AF48" t="n">
-        <v>31.87060939425737</v>
+        <v>45.84889251746262</v>
       </c>
       <c r="AG48" t="n">
-        <v>45.84889251746262</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
       </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="n">
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="n">
         <v>4.84</v>
       </c>
-      <c r="AP48" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP48" t="n">
+        <v>5.96</v>
+      </c>
       <c r="AQ48" t="n">
-        <v>5.96</v>
+        <v>5.53</v>
       </c>
       <c r="AR48" t="n">
-        <v>5.53</v>
+        <v>14.89166743732671</v>
       </c>
     </row>
     <row r="49">
@@ -6894,52 +6788,50 @@
         <v>7076952.634272937</v>
       </c>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T49" t="n">
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>5.575522840912583</v>
       </c>
       <c r="V49" t="n">
-        <v>5.575522840912583</v>
+        <v>9.402665677020261</v>
       </c>
       <c r="W49" t="n">
-        <v>9.402665677020261</v>
+        <v>-1.849416110505098</v>
       </c>
       <c r="X49" t="n">
-        <v>-1.849416110505098</v>
+        <v>9.027303488048076</v>
       </c>
       <c r="Y49" t="n">
+        <v>0.189166666666666</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>6677.770264888889</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-11.49751767837556</v>
+      </c>
+      <c r="AB49" t="n">
         <v>9.027303488048076</v>
       </c>
-      <c r="Z49" t="n">
-        <v>0.189166666666666</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>6677.770264888889</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-11.49751767837556</v>
-      </c>
       <c r="AC49" t="n">
-        <v>9.027303488048076</v>
+        <v>2.820636821381409</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.820636821381409</v>
+        <v>4450584.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>4450584.2</v>
+        <v>33.7189149235734</v>
       </c>
       <c r="AF49" t="n">
-        <v>33.7189149235734</v>
+        <v>43.70874951652414</v>
       </c>
       <c r="AG49" t="n">
-        <v>43.70874951652414</v>
+        <v>4</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6948,28 +6840,28 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="n">
         <v>6.9</v>
       </c>
-      <c r="AP49" t="inlineStr">
+      <c r="AO49" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP49" t="n">
+        <v>4.84</v>
+      </c>
       <c r="AQ49" t="n">
-        <v>4.84</v>
+        <v>4.45</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.45</v>
+        <v>15.0018830511869</v>
       </c>
     </row>
     <row r="50">
@@ -7032,55 +6924,53 @@
       <c r="S50" t="n">
         <v>6.580792833200877</v>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T50" t="n">
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>8.440460158914931</v>
       </c>
       <c r="V50" t="n">
-        <v>8.440460158914931</v>
+        <v>-6.986558027968403</v>
       </c>
       <c r="W50" t="n">
-        <v>-6.986558027968403</v>
+        <v>18.04302219856271</v>
       </c>
       <c r="X50" t="n">
-        <v>18.04302219856271</v>
+        <v>13.36118620621058</v>
       </c>
       <c r="Y50" t="n">
+        <v>1.873333333333334</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>6437.572567777778</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-26.54607227559894</v>
+      </c>
+      <c r="AB50" t="n">
         <v>13.36118620621058</v>
       </c>
-      <c r="Z50" t="n">
-        <v>1.873333333333334</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>6437.572567777778</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-26.54607227559894</v>
-      </c>
       <c r="AC50" t="n">
-        <v>13.36118620621058</v>
+        <v>8.734519539543918</v>
       </c>
       <c r="AD50" t="n">
-        <v>8.734519539543918</v>
+        <v>3935031</v>
       </c>
       <c r="AE50" t="n">
-        <v>3935031</v>
+        <v>36.5832873997689</v>
       </c>
       <c r="AF50" t="n">
-        <v>36.5832873997689</v>
+        <v>49.81097226425917</v>
       </c>
       <c r="AG50" t="n">
-        <v>49.81097226425917</v>
+        <v>1</v>
       </c>
       <c r="AH50" t="n">
         <v>1</v>
       </c>
       <c r="AI50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
@@ -7092,24 +6982,24 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>-3.079207166799123</v>
       </c>
       <c r="AN50" t="n">
-        <v>-3.079207166799123</v>
-      </c>
-      <c r="AO50" t="n">
         <v>9.66</v>
       </c>
-      <c r="AP50" t="inlineStr">
+      <c r="AO50" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP50" t="n">
+        <v>6.9</v>
+      </c>
       <c r="AQ50" t="n">
-        <v>6.9</v>
+        <v>13.49</v>
       </c>
       <c r="AR50" t="n">
-        <v>13.49</v>
+        <v>18.3810683044001</v>
       </c>
     </row>
     <row r="51">
@@ -7172,58 +7062,56 @@
       <c r="S51" t="n">
         <v>7.63587673855175</v>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T51" t="n">
+        <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>11.71159822306986</v>
       </c>
       <c r="V51" t="n">
-        <v>11.71159822306986</v>
+        <v>4.589515677491596</v>
       </c>
       <c r="W51" t="n">
-        <v>4.589515677491596</v>
+        <v>14.29536001327434</v>
       </c>
       <c r="X51" t="n">
-        <v>14.29536001327434</v>
+        <v>11.53805080852743</v>
       </c>
       <c r="Y51" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>7163.454256000002</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-10.86381606586405</v>
+      </c>
+      <c r="AB51" t="n">
         <v>11.53805080852743</v>
       </c>
-      <c r="Z51" t="n">
-        <v>0.07000000000000028</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>7163.454256000002</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-10.86381606586405</v>
-      </c>
       <c r="AC51" t="n">
-        <v>11.53805080852743</v>
+        <v>5.108050808527434</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.108050808527434</v>
+        <v>4021156.500000001</v>
       </c>
       <c r="AE51" t="n">
-        <v>4021156.500000001</v>
+        <v>36.29959192088145</v>
       </c>
       <c r="AF51" t="n">
-        <v>36.29959192088145</v>
+        <v>52.64257434397292</v>
       </c>
       <c r="AG51" t="n">
-        <v>52.64257434397292</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
@@ -7232,24 +7120,24 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>-1.70412326144825</v>
       </c>
       <c r="AN51" t="n">
-        <v>-1.70412326144825</v>
-      </c>
-      <c r="AO51" t="n">
         <v>9.34</v>
       </c>
-      <c r="AP51" t="inlineStr">
+      <c r="AO51" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP51" t="n">
+        <v>9.66</v>
+      </c>
       <c r="AQ51" t="n">
-        <v>9.66</v>
+        <v>5.96</v>
       </c>
       <c r="AR51" t="n">
-        <v>5.96</v>
+        <v>19.96408869322233</v>
       </c>
     </row>
     <row r="52">
@@ -7312,84 +7200,82 @@
       <c r="S52" t="n">
         <v>7.089103054432377</v>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T52" t="n">
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>9.343631400246831</v>
       </c>
       <c r="V52" t="n">
-        <v>9.343631400246831</v>
+        <v>2.950118842539085</v>
       </c>
       <c r="W52" t="n">
-        <v>2.950118842539085</v>
+        <v>11.31244619409408</v>
       </c>
       <c r="X52" t="n">
-        <v>11.31244619409408</v>
+        <v>11.51935465158569</v>
       </c>
       <c r="Y52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>6971.697782222222</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-4.23222223195584</v>
+      </c>
+      <c r="AB52" t="n">
         <v>11.51935465158569</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>6971.697782222222</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-4.23222223195584</v>
-      </c>
       <c r="AC52" t="n">
-        <v>11.51935465158569</v>
+        <v>6.14935465158569</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.14935465158569</v>
+        <v>4277867</v>
       </c>
       <c r="AE52" t="n">
-        <v>4277867</v>
+        <v>33.30215969781202</v>
       </c>
       <c r="AF52" t="n">
-        <v>33.30215969781202</v>
+        <v>46.97804536700182</v>
       </c>
       <c r="AG52" t="n">
-        <v>46.97804536700182</v>
+        <v>3</v>
       </c>
       <c r="AH52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>-2.420896945567622</v>
       </c>
       <c r="AN52" t="n">
-        <v>-2.420896945567622</v>
-      </c>
-      <c r="AO52" t="n">
         <v>9.51</v>
       </c>
-      <c r="AP52" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP52" t="n">
+        <v>9.34</v>
+      </c>
       <c r="AQ52" t="n">
-        <v>9.34</v>
+        <v>4.84</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.84</v>
+        <v>19.95280860197066</v>
       </c>
     </row>
     <row r="53">
@@ -7452,52 +7338,50 @@
       <c r="S53" t="n">
         <v>7.510228517697048</v>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T53" t="n">
+        <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>6.04723684532309</v>
       </c>
       <c r="V53" t="n">
-        <v>6.04723684532309</v>
+        <v>7.672107258236927</v>
       </c>
       <c r="W53" t="n">
-        <v>7.672107258236927</v>
+        <v>11.35988918487037</v>
       </c>
       <c r="X53" t="n">
-        <v>11.35988918487037</v>
+        <v>11.61890430625601</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.486666666666667</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>6891.550958</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.201378373783692</v>
+      </c>
+      <c r="AB53" t="n">
         <v>11.61890430625601</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1.486666666666667</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>6891.550958</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>3.201378373783692</v>
-      </c>
       <c r="AC53" t="n">
-        <v>11.61890430625601</v>
+        <v>6.605570972922673</v>
       </c>
       <c r="AD53" t="n">
-        <v>6.605570972922673</v>
+        <v>4692563.199999999</v>
       </c>
       <c r="AE53" t="n">
-        <v>4692563.199999999</v>
+        <v>33.91406427941131</v>
       </c>
       <c r="AF53" t="n">
-        <v>33.91406427941131</v>
+        <v>45.38101905585417</v>
       </c>
       <c r="AG53" t="n">
-        <v>45.38101905585417</v>
+        <v>4</v>
       </c>
       <c r="AH53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7506,30 +7390,30 @@
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>-0.8397714823029512</v>
       </c>
       <c r="AN53" t="n">
-        <v>-0.8397714823029512</v>
-      </c>
-      <c r="AO53" t="n">
         <v>8.35</v>
       </c>
-      <c r="AP53" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP53" t="n">
+        <v>9.51</v>
+      </c>
       <c r="AQ53" t="n">
-        <v>9.51</v>
+        <v>6.9</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.9</v>
+        <v>20.16000846400059</v>
       </c>
     </row>
     <row r="54">
@@ -7592,55 +7476,53 @@
       <c r="S54" t="n">
         <v>7.456116392886325</v>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T54" t="n">
+        <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>6.650126006928359</v>
       </c>
       <c r="V54" t="n">
-        <v>6.650126006928359</v>
+        <v>8.292078154667792</v>
       </c>
       <c r="W54" t="n">
-        <v>8.292078154667792</v>
+        <v>-1.556099321210525</v>
       </c>
       <c r="X54" t="n">
-        <v>-1.556099321210525</v>
+        <v>10.10195024932521</v>
       </c>
       <c r="Y54" t="n">
+        <v>1.596666666666667</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>7062.786664333333</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>9.711954156213508</v>
+      </c>
+      <c r="AB54" t="n">
         <v>10.10195024932521</v>
       </c>
-      <c r="Z54" t="n">
-        <v>1.596666666666667</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>7062.786664333333</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>9.711954156213508</v>
-      </c>
       <c r="AC54" t="n">
-        <v>10.10195024932521</v>
+        <v>5.198616915991876</v>
       </c>
       <c r="AD54" t="n">
-        <v>5.198616915991876</v>
+        <v>4311041</v>
       </c>
       <c r="AE54" t="n">
-        <v>4311041</v>
+        <v>35.61312685265577</v>
       </c>
       <c r="AF54" t="n">
-        <v>35.61312685265577</v>
+        <v>46.69163434075436</v>
       </c>
       <c r="AG54" t="n">
-        <v>46.69163434075436</v>
+        <v>1</v>
       </c>
       <c r="AH54" t="n">
         <v>1</v>
       </c>
       <c r="AI54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
         <v>0</v>
@@ -7652,24 +7534,24 @@
         <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>0.9461163928863252</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.9461163928863252</v>
-      </c>
-      <c r="AO54" t="n">
         <v>6.51</v>
       </c>
-      <c r="AP54" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP54" t="n">
+        <v>8.35</v>
+      </c>
       <c r="AQ54" t="n">
-        <v>8.35</v>
+        <v>9.66</v>
       </c>
       <c r="AR54" t="n">
-        <v>9.66</v>
+        <v>17.39682608410902</v>
       </c>
     </row>
     <row r="55">
@@ -7732,58 +7614,56 @@
       <c r="S55" t="n">
         <v>6.585873919801788</v>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T55" t="n">
+        <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>6.70290150455235</v>
       </c>
       <c r="V55" t="n">
-        <v>6.70290150455235</v>
+        <v>3.026878745606587</v>
       </c>
       <c r="W55" t="n">
-        <v>3.026878745606587</v>
+        <v>1.042710081260312</v>
       </c>
       <c r="X55" t="n">
-        <v>1.042710081260312</v>
+        <v>10.42373724508627</v>
       </c>
       <c r="Y55" t="n">
+        <v>2.253333333333333</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>6688.188597333333</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-6.634587751692466</v>
+      </c>
+      <c r="AB55" t="n">
         <v>10.42373724508627</v>
       </c>
-      <c r="Z55" t="n">
-        <v>2.253333333333333</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>6688.188597333333</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>-6.634587751692466</v>
-      </c>
       <c r="AC55" t="n">
-        <v>10.42373724508627</v>
+        <v>6.177070578419605</v>
       </c>
       <c r="AD55" t="n">
-        <v>6.177070578419605</v>
+        <v>4304356.3</v>
       </c>
       <c r="AE55" t="n">
-        <v>4304356.3</v>
+        <v>36.18434654212989</v>
       </c>
       <c r="AF55" t="n">
-        <v>36.18434654212989</v>
+        <v>50.13544069295565</v>
       </c>
       <c r="AG55" t="n">
-        <v>50.13544069295565</v>
+        <v>2</v>
       </c>
       <c r="AH55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
         <v>0</v>
@@ -7792,24 +7672,24 @@
         <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>0.9758739198017876</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.9758739198017876</v>
-      </c>
-      <c r="AO55" t="n">
         <v>5.61</v>
       </c>
-      <c r="AP55" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP55" t="n">
+        <v>6.51</v>
+      </c>
       <c r="AQ55" t="n">
-        <v>6.51</v>
+        <v>9.34</v>
       </c>
       <c r="AR55" t="n">
-        <v>9.34</v>
+        <v>13.02684232700213</v>
       </c>
     </row>
     <row r="56">
@@ -7872,84 +7752,82 @@
       <c r="S56" t="n">
         <v>7.360324991209977</v>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T56" t="n">
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>5.23031335818811</v>
       </c>
       <c r="V56" t="n">
-        <v>5.23031335818811</v>
+        <v>10.80198115326656</v>
       </c>
       <c r="W56" t="n">
-        <v>10.80198115326656</v>
+        <v>-2.067296627697379</v>
       </c>
       <c r="X56" t="n">
-        <v>-2.067296627697379</v>
+        <v>9.033767617571421</v>
       </c>
       <c r="Y56" t="n">
+        <v>0.8633333333333333</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>6301.844620444444</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-9.608178419407388</v>
+      </c>
+      <c r="AB56" t="n">
         <v>9.033767617571421</v>
       </c>
-      <c r="Z56" t="n">
-        <v>0.8633333333333333</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>6301.844620444444</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-9.608178419407388</v>
-      </c>
       <c r="AC56" t="n">
-        <v>9.033767617571421</v>
+        <v>3.397100950904754</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.397100950904754</v>
+        <v>4722716.2</v>
       </c>
       <c r="AE56" t="n">
-        <v>4722716.2</v>
+        <v>31.74305286436648</v>
       </c>
       <c r="AF56" t="n">
-        <v>31.74305286436648</v>
+        <v>44.2463449317577</v>
       </c>
       <c r="AG56" t="n">
-        <v>44.2463449317577</v>
+        <v>3</v>
       </c>
       <c r="AH56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>0.9903249912099765</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.9903249912099765</v>
-      </c>
-      <c r="AO56" t="n">
         <v>6.37</v>
       </c>
-      <c r="AP56" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP56" t="n">
+        <v>5.61</v>
+      </c>
       <c r="AQ56" t="n">
-        <v>5.61</v>
+        <v>9.51</v>
       </c>
       <c r="AR56" t="n">
-        <v>9.51</v>
+        <v>11.1583746011608</v>
       </c>
     </row>
     <row r="57">
@@ -8012,52 +7890,50 @@
       <c r="S57" t="n">
         <v>6.981049959495578</v>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T57" t="n">
+        <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>9.407285444637559</v>
       </c>
       <c r="V57" t="n">
-        <v>9.407285444637559</v>
+        <v>3.851762950021231</v>
       </c>
       <c r="W57" t="n">
-        <v>3.851762950021231</v>
+        <v>-12.67180548452658</v>
       </c>
       <c r="X57" t="n">
-        <v>-12.67180548452658</v>
+        <v>9.409550124407385</v>
       </c>
       <c r="Y57" t="n">
+        <v>2.614523809523811</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>6569.430029333333</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-4.674142738402532</v>
+      </c>
+      <c r="AB57" t="n">
         <v>9.409550124407385</v>
       </c>
-      <c r="Z57" t="n">
-        <v>2.614523809523811</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>6569.430029333333</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>-4.674142738402532</v>
-      </c>
       <c r="AC57" t="n">
-        <v>9.409550124407385</v>
+        <v>5.672883457740719</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.672883457740719</v>
+        <v>5160987.6</v>
       </c>
       <c r="AE57" t="n">
-        <v>5160987.6</v>
+        <v>33.73676193292928</v>
       </c>
       <c r="AF57" t="n">
-        <v>33.73676193292928</v>
+        <v>39.46831416529658</v>
       </c>
       <c r="AG57" t="n">
-        <v>39.46831416529658</v>
+        <v>4</v>
       </c>
       <c r="AH57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -8066,30 +7942,30 @@
         <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>-0.3989500405044222</v>
       </c>
       <c r="AN57" t="n">
-        <v>-0.3989500405044222</v>
-      </c>
-      <c r="AO57" t="n">
         <v>7.38</v>
       </c>
-      <c r="AP57" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP57" t="n">
+        <v>6.37</v>
+      </c>
       <c r="AQ57" t="n">
-        <v>6.37</v>
+        <v>8.35</v>
       </c>
       <c r="AR57" t="n">
-        <v>8.35</v>
+        <v>11.02598785965252</v>
       </c>
     </row>
     <row r="58">
@@ -8152,55 +8028,53 @@
       <c r="S58" t="n">
         <v>6.818175531841941</v>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T58" t="n">
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>7.819277904951916</v>
       </c>
       <c r="V58" t="n">
-        <v>7.819277904951916</v>
+        <v>6.329413873184042</v>
       </c>
       <c r="W58" t="n">
-        <v>6.329413873184042</v>
+        <v>10.87757853879581</v>
       </c>
       <c r="X58" t="n">
-        <v>10.87757853879581</v>
+        <v>9.458110952394904</v>
       </c>
       <c r="Y58" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>5818.067809555556</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-17.62362243027297</v>
+      </c>
+      <c r="AB58" t="n">
         <v>9.458110952394904</v>
       </c>
-      <c r="Z58" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>5818.067809555556</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>-17.62362243027297</v>
-      </c>
       <c r="AC58" t="n">
-        <v>9.458110952394904</v>
+        <v>6.76477761906157</v>
       </c>
       <c r="AD58" t="n">
-        <v>6.76477761906157</v>
+        <v>4579756.300000001</v>
       </c>
       <c r="AE58" t="n">
-        <v>4579756.300000001</v>
+        <v>36.14484028331376</v>
       </c>
       <c r="AF58" t="n">
-        <v>36.14484028331376</v>
+        <v>47.82306866415576</v>
       </c>
       <c r="AG58" t="n">
-        <v>47.82306866415576</v>
+        <v>1</v>
       </c>
       <c r="AH58" t="n">
         <v>1</v>
       </c>
       <c r="AI58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
         <v>0</v>
@@ -8212,24 +8086,24 @@
         <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>-0.9918244681580584</v>
       </c>
       <c r="AN58" t="n">
-        <v>-0.9918244681580584</v>
-      </c>
-      <c r="AO58" t="n">
         <v>7.81</v>
       </c>
-      <c r="AP58" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP58" t="n">
+        <v>7.38</v>
+      </c>
       <c r="AQ58" t="n">
-        <v>7.38</v>
+        <v>6.51</v>
       </c>
       <c r="AR58" t="n">
-        <v>6.51</v>
+        <v>9.476302029641426</v>
       </c>
     </row>
     <row r="59">
@@ -8292,58 +8166,56 @@
       <c r="S59" t="n">
         <v>8.348627848902201</v>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
+      <c r="T59" t="n">
+        <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>7.333911095656176</v>
       </c>
       <c r="V59" t="n">
-        <v>7.333911095656176</v>
+        <v>5.585101474270227</v>
       </c>
       <c r="W59" t="n">
-        <v>5.585101474270227</v>
+        <v>12.75204768450591</v>
       </c>
       <c r="X59" t="n">
-        <v>12.75204768450591</v>
+        <v>9.231437233294981</v>
       </c>
       <c r="Y59" t="n">
+        <v>3.793333333333333</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>6022.068182222222</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-9.959653580592832</v>
+      </c>
+      <c r="AB59" t="n">
         <v>9.231437233294981</v>
       </c>
-      <c r="Z59" t="n">
-        <v>3.793333333333333</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>6022.068182222222</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>-9.959653580592832</v>
-      </c>
       <c r="AC59" t="n">
-        <v>9.231437233294981</v>
+        <v>7.524770566628314</v>
       </c>
       <c r="AD59" t="n">
-        <v>7.524770566628314</v>
+        <v>4514543.4</v>
       </c>
       <c r="AE59" t="n">
-        <v>4514543.4</v>
+        <v>37.02985998539742</v>
       </c>
       <c r="AF59" t="n">
-        <v>37.02985998539742</v>
+        <v>52.32284177398759</v>
       </c>
       <c r="AG59" t="n">
-        <v>52.32284177398759</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
         <v>0</v>
@@ -8352,24 +8224,24 @@
         <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>0.1186278489022001</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.1186278489022001</v>
-      </c>
-      <c r="AO59" t="n">
         <v>8.23</v>
       </c>
-      <c r="AP59" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
+      <c r="AP59" t="n">
+        <v>7.81</v>
+      </c>
       <c r="AQ59" t="n">
-        <v>7.81</v>
+        <v>5.61</v>
       </c>
       <c r="AR59" t="n">
-        <v>5.61</v>
+        <v>10.3813332654406</v>
       </c>
     </row>
     <row r="60">
@@ -8416,76 +8288,68 @@
       <c r="S60" t="n">
         <v>7.963217799958411</v>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>11.51296451558743</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0.06211801696809349</v>
-      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
-        <v>26.05515648436114</v>
+        <v>12.11115462536545</v>
       </c>
       <c r="Y60" t="n">
+        <v>4.664086021505375</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>5669.842256</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-10.02884714729559</v>
+      </c>
+      <c r="AB60" t="n">
         <v>12.11115462536545</v>
       </c>
-      <c r="Z60" t="n">
-        <v>4.664086021505375</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>5669.842256</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>-10.02884714729559</v>
-      </c>
       <c r="AC60" t="n">
-        <v>12.11115462536545</v>
-      </c>
-      <c r="AD60" t="n">
         <v>11.34782129203212</v>
       </c>
+      <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
+      <c r="AG60" t="n">
+        <v>3</v>
+      </c>
       <c r="AH60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
       </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="n">
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="n">
         <v>7.963217799958411</v>
       </c>
-      <c r="AP60" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>2022-23 base (spliced)</t>
         </is>
       </c>
+      <c r="AP60" t="n">
+        <v>8.23</v>
+      </c>
       <c r="AQ60" t="n">
-        <v>8.23</v>
+        <v>6.37</v>
       </c>
       <c r="AR60" t="n">
-        <v>6.37</v>
+        <v>9.302904820121238</v>
       </c>
     </row>
     <row r="61">
@@ -8532,46 +8396,38 @@
       <c r="S61" t="n">
         <v>7.832162523284558</v>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="n">
-        <v>-3.987077277254847</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-6.038860235698918</v>
-      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
-        <v>42.53043712334237</v>
+        <v>10.65310701519588</v>
       </c>
       <c r="Y61" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>7333.314248222222</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>11.62786140468883</v>
+      </c>
+      <c r="AB61" t="n">
         <v>10.65310701519588</v>
       </c>
-      <c r="Z61" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>7333.314248222222</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>11.62786140468883</v>
-      </c>
       <c r="AC61" t="n">
-        <v>10.65310701519588</v>
-      </c>
-      <c r="AD61" t="n">
         <v>7.533107015195885</v>
       </c>
+      <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AG61" t="n">
+        <v>4</v>
+      </c>
       <c r="AH61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8580,28 +8436,28 @@
         <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="n">
         <v>7.832162523284558</v>
       </c>
-      <c r="AP61" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>2022-23 base (spliced)</t>
         </is>
       </c>
+      <c r="AP61" t="n">
+        <v>7.963217799958411</v>
+      </c>
       <c r="AQ61" t="n">
-        <v>7.963217799958411</v>
+        <v>7.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>7.38</v>
+        <v>17.07920091983608</v>
       </c>
     </row>
     <row r="62">
@@ -8636,45 +8492,37 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0.9897328992809706</v>
-      </c>
-      <c r="W62" t="n">
-        <v>7.463283166278045</v>
-      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
-        <v>8.16213631315421</v>
-      </c>
-      <c r="Y62" t="n">
         <v>10.39133638585295</v>
       </c>
-      <c r="Z62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="n">
+        <v>10612.60457775</v>
+      </c>
       <c r="AA62" t="n">
-        <v>10612.60457775</v>
+        <v>82.4077155016985</v>
       </c>
       <c r="AB62" t="n">
-        <v>82.4077155016985</v>
-      </c>
-      <c r="AC62" t="n">
         <v>10.39133638585295</v>
       </c>
+      <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AG62" t="n">
+        <v>1</v>
+      </c>
       <c r="AH62" t="n">
         <v>1</v>
       </c>
       <c r="AI62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
         <v>0</v>
@@ -8685,21 +8533,21 @@
       <c r="AL62" t="n">
         <v>0</v>
       </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AP62" t="n">
+        <v>7.832162523284558</v>
+      </c>
       <c r="AQ62" t="n">
-        <v>7.832162523284558</v>
+        <v>7.81</v>
       </c>
       <c r="AR62" t="n">
-        <v>7.81</v>
+        <v>16.38629288719908</v>
       </c>
     </row>
     <row r="63">
@@ -8726,46 +8574,32 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>9.924756625352526</v>
-      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="n">
-        <v>76.22856893383445</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>9.924756625352526</v>
-      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
+      <c r="AG63" t="n">
+        <v>2</v>
+      </c>
       <c r="AH63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
         <v>0</v>
@@ -8773,20 +8607,18 @@
       <c r="AL63" t="n">
         <v>0</v>
       </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="n">
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="n">
         <v>8.23</v>
       </c>
+      <c r="AR63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/composite_master_quarterly.xlsx
+++ b/data/processed/composite_master_quarterly.xlsx
@@ -8484,7 +8484,7 @@
         <v>1.447659713123209</v>
       </c>
       <c r="O62" t="n">
-        <v>112.215</v>
+        <v>103.2766666666667</v>
       </c>
       <c r="P62" t="n">
         <v>31163977.2819288</v>
@@ -8503,10 +8503,10 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>10612.60457775</v>
+        <v>9767.271981833333</v>
       </c>
       <c r="AA62" t="n">
-        <v>82.4077155016985</v>
+        <v>67.87827680164935</v>
       </c>
       <c r="AB62" t="n">
         <v>10.39133638585295</v>
@@ -8569,7 +8569,9 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>87.42</v>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>

--- a/data/processed/composite_master_quarterly.xlsx
+++ b/data/processed/composite_master_quarterly.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR63"/>
+  <dimension ref="A1:AW64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,125 +514,150 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>PFCE_new</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>GFCE_new</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>GFCF_new</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Exports_new</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Imports_new</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_new_base</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>GFCF_YoY</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Exports_YoY</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Imports_YoY</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>M3_level_YoY</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>RealRate</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>CrudeINR</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>CrudeINR_YoY</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>M3_growth_YoY</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>RealM3_YoY</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>GDP_proxy_old</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>InvestmentRate</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>TradeOpenness</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>COVID</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>BaseRevision_gap</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>GDP_growth</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>GDP_growth_source</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>GDP_growth_lag1</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>GDP_growth_lag4</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>BankCredit_YoY</t>
         </is>
@@ -688,57 +713,62 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>5247.091272</v>
-      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>5247.091272</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
         <v>2000784.9</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AJ2" t="n">
         <v>34.83406936947595</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AK2" t="n">
         <v>57.51108977281867</v>
       </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
       <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
         <v>20.68093134213473</v>
       </c>
     </row>
@@ -792,57 +822,62 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>5188.316065999999</v>
-      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>5188.316065999999</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
         <v>1978744.1</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AJ3" t="n">
         <v>36.77832317983917</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AK3" t="n">
         <v>58.00764232221842</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AL3" t="n">
         <v>2</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr">
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
         <v>19.54897231033894</v>
       </c>
     </row>
@@ -896,57 +931,62 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>5571.615992</v>
-      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>5571.615992</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
         <v>2077054.9</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AJ4" t="n">
         <v>36.21289451713577</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
         <v>61.02004333154603</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AL4" t="n">
         <v>3</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr">
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
         <v>15.97466886934438</v>
       </c>
     </row>
@@ -1002,59 +1042,64 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>0.7199999999999998</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5957.187441333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
+        <v>0.7199999999999998</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5957.187441333333</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
         <v>2248347.9</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AJ5" t="n">
         <v>36.5097945918423</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AK5" t="n">
         <v>57.53421434467503</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AL5" t="n">
         <v>4</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
         <v>16.99023695512736</v>
       </c>
     </row>
@@ -1114,75 +1159,80 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
         <v>9.575513361842125</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AA6" t="n">
         <v>5.111637788934331</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AB6" t="n">
         <v>5.267624749866529</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AC6" t="n">
         <v>15.82326235219023</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AD6" t="n">
         <v>-1.814444444444446</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AE6" t="n">
         <v>5865.912661111111</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AF6" t="n">
         <v>11.79360824945666</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AG6" t="n">
         <v>15.82326235219023</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AH6" t="n">
         <v>5.919929018856893</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AI6" t="n">
         <v>2072727.7</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AJ6" t="n">
         <v>36.84477222936713</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AK6" t="n">
         <v>58.40109629451084</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
       <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
       <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
         <v>4.87</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
         <v>19.04844621955139</v>
       </c>
     </row>
@@ -1242,77 +1292,82 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>5.42578628425272</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AA7" t="n">
         <v>28.60116106573245</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AB7" t="n">
         <v>16.35569848350134</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AC7" t="n">
         <v>13.63341342336888</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AD7" t="n">
         <v>-2.026666666666666</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AE7" t="n">
         <v>6052.851920444445</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AF7" t="n">
         <v>16.66313006853821</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AG7" t="n">
         <v>13.63341342336888</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AH7" t="n">
         <v>3.606746756702213</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AI7" t="n">
         <v>2185184.4</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AJ7" t="n">
         <v>35.11076685336029</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AK7" t="n">
         <v>63.96095908427682</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AL7" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
       <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
         <v>7.49</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AU7" t="n">
         <v>4.87</v>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
         <v>16.33561091824198</v>
       </c>
     </row>
@@ -1372,77 +1427,82 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.283711069042749</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AA8" t="n">
         <v>-4.49552591945932</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AB8" t="n">
         <v>3.097123125456802</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AC8" t="n">
         <v>11.24888299217723</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AD8" t="n">
         <v>-1.763333333333334</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AE8" t="n">
         <v>5961.101261111111</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AF8" t="n">
         <v>6.990526082026349</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
         <v>11.24888299217723</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AH8" t="n">
         <v>1.485549658843899</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AI8" t="n">
         <v>2128943.1</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AJ8" t="n">
         <v>36.13712832437842</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AK8" t="n">
         <v>59.40262565025811</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AL8" t="n">
         <v>3</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
       <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
         <v>5.38</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AU8" t="n">
         <v>7.49</v>
       </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
         <v>15.09073998649066</v>
       </c>
     </row>
@@ -1502,77 +1562,82 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.004176558644334</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AA9" t="n">
         <v>-0.03185422286192674</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AB9" t="n">
         <v>0.3793396929364645</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AC9" t="n">
         <v>13.91723013647719</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AD9" t="n">
         <v>-2.106344086021505</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AE9" t="n">
         <v>6093.205149777778</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AF9" t="n">
         <v>2.283253796929396</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AG9" t="n">
         <v>13.91723013647719</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AH9" t="n">
         <v>4.02056346981052</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AI9" t="n">
         <v>2323049.3</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AJ9" t="n">
         <v>36.39731192962629</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AK9" t="n">
         <v>55.79331872121698</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AL9" t="n">
         <v>4</v>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
       <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AU9" t="n">
         <v>5.38</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
         <v>14.06391082060408</v>
       </c>
     </row>
@@ -1632,79 +1697,84 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.858888886851996</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AA10" t="n">
         <v>3.294761157642023</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AB10" t="n">
         <v>-3.00363159040995</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AC10" t="n">
         <v>12.69099146058279</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AD10" t="n">
         <v>-1.471290322580646</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AE10" t="n">
         <v>5736.900974888889</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AF10" t="n">
         <v>-2.199345501298089</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AG10" t="n">
         <v>12.69099146058279</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AH10" t="n">
         <v>3.88099146058279</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AI10" t="n">
         <v>2272050.6</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AJ10" t="n">
         <v>34.57338934264932</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AK10" t="n">
         <v>53.15432675663122</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
       <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
         <v>6.45</v>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AU10" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AV10" t="n">
         <v>4.87</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AW10" t="n">
         <v>13.4687945083054</v>
       </c>
     </row>
@@ -1764,79 +1834,84 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.620768082790791</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AA11" t="n">
         <v>-1.099745006218456</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AB11" t="n">
         <v>-8.164754685887843</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
         <v>13.0042499150413</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AD11" t="n">
         <v>-2.809444444444444</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AE11" t="n">
         <v>6863.803933666666</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AF11" t="n">
         <v>13.39784987111787</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AG11" t="n">
         <v>13.0042499150413</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
         <v>2.914249915041299</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AI11" t="n">
         <v>2318883.3</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AJ11" t="n">
         <v>33.62265362814938</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AK11" t="n">
         <v>57.33926325658562</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AL11" t="n">
         <v>2</v>
       </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
       <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
         <v>7.34</v>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AU11" t="n">
         <v>6.45</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AV11" t="n">
         <v>7.49</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AW11" t="n">
         <v>17.59710763661637</v>
       </c>
     </row>
@@ -1896,79 +1971,84 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.370827732745595</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AA12" t="n">
         <v>16.12191446918512</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AB12" t="n">
         <v>-14.06065989558057</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AC12" t="n">
         <v>14.80433839943327</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AD12" t="n">
         <v>-2.918602150537635</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AE12" t="n">
         <v>6776.804489666667</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AF12" t="n">
         <v>13.68376735817291</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AG12" t="n">
         <v>14.80433839943327</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
         <v>4.211005066099936</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AI12" t="n">
         <v>2437481</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AJ12" t="n">
         <v>32.31116878449514</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AK12" t="n">
         <v>51.13394935181033</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AL12" t="n">
         <v>3</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
       <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
         <v>6.53</v>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AU12" t="n">
         <v>7.34</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AV12" t="n">
         <v>5.38</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AW12" t="n">
         <v>14.23574573868303</v>
       </c>
     </row>
@@ -2028,79 +2108,84 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.3993719896750902</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AA13" t="n">
         <v>14.37529254566316</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AB13" t="n">
         <v>-6.919657925902833</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AC13" t="n">
         <v>13.43971225818972</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AD13" t="n">
         <v>-0.315913978494625</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AE13" t="n">
         <v>6682.680888888889</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AF13" t="n">
         <v>9.674313019521573</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AG13" t="n">
         <v>13.43971225818972</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AH13" t="n">
         <v>5.196378924856385</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AI13" t="n">
         <v>2527377.6</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AJ13" t="n">
         <v>33.32112700531966</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AK13" t="n">
         <v>52.58889688663855</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AL13" t="n">
         <v>4</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
       <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
         <v>5.34</v>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP13" t="n">
+      <c r="AU13" t="n">
         <v>6.53</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AV13" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AW13" t="n">
         <v>13.94625906295703</v>
       </c>
     </row>
@@ -2160,79 +2245,84 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.933630748051397</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AA14" t="n">
         <v>13.11119259760236</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AB14" t="n">
         <v>0.8886256825372474</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AC14" t="n">
         <v>11.82382177147869</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AD14" t="n">
         <v>0.1400000000000006</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AE14" t="n">
         <v>6559.778436666667</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AF14" t="n">
         <v>14.34358838298957</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AG14" t="n">
         <v>11.82382177147869</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
         <v>3.963821771478694</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AI14" t="n">
         <v>2463577.7</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AJ14" t="n">
         <v>32.82093761442961</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AK14" t="n">
         <v>52.18790135987997</v>
       </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
       <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
       <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
         <v>8.02</v>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP14" t="n">
+      <c r="AU14" t="n">
         <v>5.34</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AV14" t="n">
         <v>6.45</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AW14" t="n">
         <v>12.77406130657064</v>
       </c>
     </row>
@@ -2292,79 +2382,84 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
         <v>4.602343991388147</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AA15" t="n">
         <v>-2.869419997361555</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AB15" t="n">
         <v>-0.4208734903458744</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AC15" t="n">
         <v>12.43756629597852</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AD15" t="n">
         <v>1.316666666666666</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AE15" t="n">
         <v>6171.128698777778</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
         <v>-10.09171068379947</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AG15" t="n">
         <v>12.43756629597852</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AH15" t="n">
         <v>5.754232962645187</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AI15" t="n">
         <v>2480862.6</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AJ15" t="n">
         <v>32.87377543601165</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AK15" t="n">
         <v>52.73325092651241</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AL15" t="n">
         <v>2</v>
       </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
       <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP15" t="n">
+      <c r="AU15" t="n">
         <v>8.02</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AV15" t="n">
         <v>7.34</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AW15" t="n">
         <v>9.211775467878791</v>
       </c>
     </row>
@@ -2424,79 +2519,84 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.7692057656213613</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AA16" t="n">
         <v>3.502283006831108</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AB16" t="n">
         <v>7.605123275071479</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AC16" t="n">
         <v>10.71072906091495</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AD16" t="n">
         <v>3.943333333333333</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AE16" t="n">
         <v>4731.892736888889</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AF16" t="n">
         <v>-30.17516228918626</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AG16" t="n">
         <v>10.71072906091495</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
         <v>6.65406239424828</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AI16" t="n">
         <v>2504877.3</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AJ16" t="n">
         <v>31.6836557223781</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AK16" t="n">
         <v>52.5368727641869</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AL16" t="n">
         <v>3</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
       <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
         <v>5.92</v>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP16" t="n">
+      <c r="AU16" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AV16" t="n">
         <v>6.53</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AW16" t="n">
         <v>10.05307330780989</v>
       </c>
     </row>
@@ -2556,79 +2656,84 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.159494731762379</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AA17" t="n">
         <v>-4.744519677206238</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AB17" t="n">
         <v>-4.182339733287</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AC17" t="n">
         <v>10.85152572374752</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AD17" t="n">
         <v>2.442365591397849</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AE17" t="n">
         <v>3355.652919444444</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AF17" t="n">
         <v>-49.78582734627062</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AG17" t="n">
         <v>10.85152572374752</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AH17" t="n">
         <v>5.581525723747524</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AI17" t="n">
         <v>2640135.4</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AJ17" t="n">
         <v>32.58684762910266</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AK17" t="n">
         <v>48.09703320519091</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AL17" t="n">
         <v>4</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
       <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
         <v>7.11</v>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP17" t="n">
+      <c r="AU17" t="n">
         <v>5.92</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AV17" t="n">
         <v>5.34</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AW17" t="n">
         <v>9.047647923575219</v>
       </c>
     </row>
@@ -2688,79 +2793,84 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.677223461241952</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AA18" t="n">
         <v>-6.429572715533838</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AB18" t="n">
         <v>-5.775424759376779</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AC18" t="n">
         <v>10.61103602271594</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AD18" t="n">
         <v>2.326111111111111</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AE18" t="n">
         <v>3915.762237333333</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AF18" t="n">
         <v>-40.30648633731726</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AG18" t="n">
         <v>10.61103602271594</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
         <v>5.517702689382602</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AI18" t="n">
         <v>2605637.4</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AJ18" t="n">
         <v>32.17263461140065</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AK18" t="n">
         <v>46.33658927370325</v>
       </c>
-      <c r="AG18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
       <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
       <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
         <v>7.59</v>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP18" t="n">
+      <c r="AU18" t="n">
         <v>7.11</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AV18" t="n">
         <v>8.02</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AW18" t="n">
         <v>8.788918414916846</v>
       </c>
     </row>
@@ -2820,79 +2930,84 @@
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.532117831185033</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AA19" t="n">
         <v>-4.741623456412802</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AB19" t="n">
         <v>-3.629079934995072</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AC19" t="n">
         <v>10.65871462781398</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AD19" t="n">
         <v>3.292222222222223</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AE19" t="n">
         <v>3263.912507777777</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AF19" t="n">
         <v>-47.10995885689096</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AG19" t="n">
         <v>10.65871462781398</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
         <v>6.712047961147315</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AI19" t="n">
         <v>2632744.4</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AJ19" t="n">
         <v>32.07145744949643</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AK19" t="n">
         <v>47.62298991121205</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AL19" t="n">
         <v>2</v>
       </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
       <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP19" t="n">
+      <c r="AU19" t="n">
         <v>7.59</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AV19" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AW19" t="n">
         <v>9.281122610061022</v>
       </c>
     </row>
@@ -2952,79 +3067,84 @@
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>10.23364972915188</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AA20" t="n">
         <v>-8.870003053492791</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AB20" t="n">
         <v>-9.743196979576163</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AC20" t="n">
         <v>10.71061117661882</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AD20" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AE20" t="n">
         <v>2872.288347333334</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AF20" t="n">
         <v>-39.29937749979943</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AG20" t="n">
         <v>10.71061117661882</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AH20" t="n">
         <v>5.370611176618823</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AI20" t="n">
         <v>2745756.2</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AJ20" t="n">
         <v>31.86206772473098</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AK20" t="n">
         <v>43.46026788540075</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AL20" t="n">
         <v>3</v>
       </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
       <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP20" t="n">
+      <c r="AU20" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AV20" t="n">
         <v>5.92</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AW20" t="n">
         <v>10.59938609872986</v>
       </c>
     </row>
@@ -3084,79 +3204,84 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
         <v>8.639615480865693</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AA21" t="n">
         <v>-2.513070406560536</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AB21" t="n">
         <v>-4.158033170070452</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AC21" t="n">
         <v>10.11782309310898</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AD21" t="n">
         <v>1.489999999999999</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AE21" t="n">
         <v>2274.658663444444</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AF21" t="n">
         <v>-32.21412589294149</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AG21" t="n">
         <v>10.11782309310898</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AH21" t="n">
         <v>4.857823093108979</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AI21" t="n">
         <v>2881008.1</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AJ21" t="n">
         <v>32.44234891252128</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AK21" t="n">
         <v>42.60152201585271</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AL21" t="n">
         <v>4</v>
       </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
       <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
         <v>9.09</v>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP21" t="n">
+      <c r="AU21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AV21" t="n">
         <v>7.11</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AW21" t="n">
         <v>10.91108580725597</v>
       </c>
     </row>
@@ -3216,79 +3341,84 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
         <v>13.74506711302919</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AA22" t="n">
         <v>3.546380318699183</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AB22" t="n">
         <v>0.4082080070155092</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AC22" t="n">
         <v>10.29374846651843</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AD22" t="n">
         <v>0.8444444444444432</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AE22" t="n">
         <v>3045.102807444444</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AF22" t="n">
         <v>-22.23473686905505</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AG22" t="n">
         <v>10.29374846651843</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AH22" t="n">
         <v>4.627081799851759</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AI22" t="n">
         <v>2851758.2</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AJ22" t="n">
         <v>33.4364743827159</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AK22" t="n">
         <v>43.15129873212954</v>
       </c>
-      <c r="AG22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
       <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
       <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
         <v>8.68</v>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP22" t="n">
+      <c r="AU22" t="n">
         <v>9.09</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AV22" t="n">
         <v>7.59</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AW22" t="n">
         <v>9.008750801642318</v>
       </c>
     </row>
@@ -3348,79 +3478,84 @@
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
         <v>8.240009143024984</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AA23" t="n">
         <v>2.457148141955234</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AB23" t="n">
         <v>-0.1052770982733375</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AC23" t="n">
         <v>13.64568713425012</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AD23" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AE23" t="n">
         <v>3065.94998488889</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AF23" t="n">
         <v>-6.065190853527803</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AG23" t="n">
         <v>13.64568713425012</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AH23" t="n">
         <v>8.475687134250117</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AI23" t="n">
         <v>2870854.4</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AJ23" t="n">
         <v>31.83494084548489</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AK23" t="n">
         <v>44.15987449589921</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AL23" t="n">
         <v>2</v>
       </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
       <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
         <v>9.67</v>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP23" t="n">
+      <c r="AU23" t="n">
         <v>8.68</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AV23" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AW23" t="n">
         <v>12.09976118372467</v>
       </c>
     </row>
@@ -3480,79 +3615,84 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
         <v>6.666855650429726</v>
       </c>
-      <c r="V24" t="n">
+      <c r="AA24" t="n">
         <v>6.875498179136375</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AB24" t="n">
         <v>10.61767341467406</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AC24" t="n">
         <v>6.20367820751595</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AD24" t="n">
         <v>2.511397849462365</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AE24" t="n">
         <v>3316.391325333333</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AF24" t="n">
         <v>15.46164327172481</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AG24" t="n">
         <v>6.20367820751595</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AH24" t="n">
         <v>2.457011540849284</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AI24" t="n">
         <v>2978751.2</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AJ24" t="n">
         <v>31.32789338028634</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AK24" t="n">
         <v>43.5870071995271</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AL24" t="n">
         <v>3</v>
       </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
       <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="n">
         <v>8.58</v>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP24" t="n">
+      <c r="AU24" t="n">
         <v>9.67</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AV24" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AW24" t="n">
         <v>4.709945027083573</v>
       </c>
     </row>
@@ -3612,79 +3752,84 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>5.591126762085352</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AA25" t="n">
         <v>7.028176335068204</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AB25" t="n">
         <v>6.982130576597823</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AC25" t="n">
         <v>10.10814030226557</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AD25" t="n">
         <v>2.68</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AE25" t="n">
         <v>3597.143322666667</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AF25" t="n">
         <v>58.13991701153198</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AG25" t="n">
         <v>10.10814030226557</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AH25" t="n">
         <v>6.538140302265568</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AI25" t="n">
         <v>3054867.5</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AJ25" t="n">
         <v>32.3066417774257</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AK25" t="n">
         <v>42.99140633759075</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AL25" t="n">
         <v>4</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
       <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
         <v>6.29</v>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP25" t="n">
+      <c r="AU25" t="n">
         <v>8.58</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AV25" t="n">
         <v>9.09</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AW25" t="n">
         <v>8.163896591586761</v>
       </c>
     </row>
@@ -3744,79 +3889,84 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.067751173170262</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AA26" t="n">
         <v>3.948631594026897</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AB26" t="n">
         <v>21.73477881766106</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AC26" t="n">
         <v>6.997780141657595</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AD26" t="n">
         <v>4.039999999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AE26" t="n">
         <v>3201.643760999999</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AF26" t="n">
         <v>5.140744449509405</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AG26" t="n">
         <v>6.997780141657595</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AH26" t="n">
         <v>4.787780141657594</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AI26" t="n">
         <v>2953345.399999999</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AJ26" t="n">
         <v>32.63108676689154</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AK26" t="n">
         <v>47.09104123073449</v>
       </c>
-      <c r="AG26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
       <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
       <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
         <v>6.11</v>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP26" t="n">
+      <c r="AU26" t="n">
         <v>6.29</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AV26" t="n">
         <v>8.68</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AW26" t="n">
         <v>5.640994972621405</v>
       </c>
     </row>
@@ -3876,79 +4026,84 @@
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
         <v>6.412776928945041</v>
       </c>
-      <c r="V27" t="n">
+      <c r="AA27" t="n">
         <v>4.654156833996614</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AB27" t="n">
         <v>10.56970803731674</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AC27" t="n">
         <v>5.559141706560822</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AD27" t="n">
         <v>3.112688172043011</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AE27" t="n">
         <v>3350.068524</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AF27" t="n">
         <v>9.266900651068743</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AG27" t="n">
         <v>5.559141706560822</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AH27" t="n">
         <v>2.585808373227489</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AI27" t="n">
         <v>2994242.5</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AJ27" t="n">
         <v>32.4804487278502</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AK27" t="n">
         <v>45.60718779457575</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AL27" t="n">
         <v>2</v>
       </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
       <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
         <v>5.32</v>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP27" t="n">
+      <c r="AU27" t="n">
         <v>6.11</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AV27" t="n">
         <v>9.67</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AW27" t="n">
         <v>6.518715167421196</v>
       </c>
     </row>
@@ -4008,79 +4163,84 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
         <v>9.265500760839295</v>
       </c>
-      <c r="V28" t="n">
+      <c r="AA28" t="n">
         <v>4.50683307705424</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AB28" t="n">
         <v>14.09341674061191</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AC28" t="n">
         <v>10.01935732644641</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AD28" t="n">
         <v>1.443333333333333</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AE28" t="n">
         <v>3982.758961999999</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AF28" t="n">
         <v>20.0931546158742</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AG28" t="n">
         <v>10.01935732644641</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AH28" t="n">
         <v>5.462690659779744</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AI28" t="n">
         <v>3103022.7</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AJ28" t="n">
         <v>32.85969516110855</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AK28" t="n">
         <v>45.82658064344808</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AL28" t="n">
         <v>3</v>
       </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="inlineStr"/>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
       <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
         <v>6.67</v>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP28" t="n">
+      <c r="AU28" t="n">
         <v>5.32</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AV28" t="n">
         <v>8.58</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AW28" t="n">
         <v>10.26152247813552</v>
       </c>
     </row>
@@ -4140,79 +4300,84 @@
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
         <v>14.21162558333961</v>
       </c>
-      <c r="V29" t="n">
+      <c r="AA29" t="n">
         <v>5.103139136687784</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AB29" t="n">
         <v>23.56981900730852</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AC29" t="n">
         <v>9.151438935891075</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AD29" t="n">
         <v>1.403333333333333</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AE29" t="n">
         <v>4298.677193555555</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AF29" t="n">
         <v>19.5025276437643</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AG29" t="n">
         <v>9.151438935891075</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AH29" t="n">
         <v>4.554772269224409</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AI29" t="n">
         <v>3231777.6</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AJ29" t="n">
         <v>34.87811785068378</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AK29" t="n">
         <v>46.47366204902218</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AL29" t="n">
         <v>4</v>
       </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
       <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="n">
         <v>8.93</v>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AT29" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP29" t="n">
+      <c r="AU29" t="n">
         <v>6.67</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AV29" t="n">
         <v>6.29</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AW29" t="n">
         <v>9.997605700656621</v>
       </c>
     </row>
@@ -4272,79 +4437,84 @@
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>14.36150778757108</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AA30" t="n">
         <v>9.135222967313727</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AB30" t="n">
         <v>5.259283367834988</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AC30" t="n">
         <v>9.756405440982574</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AD30" t="n">
         <v>1.279444444444444</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AE30" t="n">
         <v>4990.7252</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AF30" t="n">
         <v>55.88009074567371</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AG30" t="n">
         <v>9.756405440982574</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AH30" t="n">
         <v>4.966405440982574</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AI30" t="n">
         <v>3244054.3</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AJ30" t="n">
         <v>33.97328460254194</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AK30" t="n">
         <v>45.87483939464268</v>
       </c>
-      <c r="AG30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
       <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
       <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="n">
         <v>7.5</v>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP30" t="n">
+      <c r="AU30" t="n">
         <v>8.93</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AV30" t="n">
         <v>6.11</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AW30" t="n">
         <v>12.81782525137924</v>
       </c>
     </row>
@@ -4404,79 +4574,84 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
         <v>12.86741547986445</v>
       </c>
-      <c r="V31" t="n">
+      <c r="AA31" t="n">
         <v>12.13194484375899</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AB31" t="n">
         <v>18.09671167835027</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AC31" t="n">
         <v>9.394318688626569</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AD31" t="n">
         <v>2.563333333333333</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AE31" t="n">
         <v>5277.047220444445</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AF31" t="n">
         <v>57.52057555358962</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AG31" t="n">
         <v>9.394318688626569</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AH31" t="n">
         <v>5.540985355293236</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AI31" t="n">
         <v>3244734.5</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AJ31" t="n">
         <v>33.82972012039814</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AK31" t="n">
         <v>48.52609666522793</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AL31" t="n">
         <v>2</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
       <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="n">
         <v>6.46</v>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AT31" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP31" t="n">
+      <c r="AU31" t="n">
         <v>7.5</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AV31" t="n">
         <v>5.32</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AW31" t="n">
         <v>12.50371788427496</v>
       </c>
     </row>
@@ -4536,79 +4711,84 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
         <v>12.84924205884448</v>
       </c>
-      <c r="V32" t="n">
+      <c r="AA32" t="n">
         <v>15.17864957504445</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AB32" t="n">
         <v>12.10749283724164</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AC32" t="n">
         <v>10.15251467325937</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AD32" t="n">
         <v>3.893333333333333</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AE32" t="n">
         <v>4880.271473777778</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AF32" t="n">
         <v>22.53494425198856</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AG32" t="n">
         <v>10.15251467325937</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AH32" t="n">
         <v>7.545848006592704</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AI32" t="n">
         <v>3390979.6</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AJ32" t="n">
         <v>33.93297618186792</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AK32" t="n">
         <v>47.59802742546727</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AL32" t="n">
         <v>3</v>
       </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="inlineStr"/>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
       <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
         <v>6.23</v>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP32" t="n">
+      <c r="AU32" t="n">
         <v>6.46</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AV32" t="n">
         <v>6.67</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AW32" t="n">
         <v>15.11314187668522</v>
       </c>
     </row>
@@ -4668,79 +4848,84 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
         <v>5.57755828866151</v>
       </c>
-      <c r="V33" t="n">
+      <c r="AA33" t="n">
         <v>11.24284224318506</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AB33" t="n">
         <v>0.7659880365536331</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AC33" t="n">
         <v>10.52441362486438</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AD33" t="n">
         <v>3.884523809523811</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AE33" t="n">
         <v>4452.080520333333</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AF33" t="n">
         <v>3.56861703892899</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AG33" t="n">
         <v>10.52441362486438</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AH33" t="n">
         <v>8.057746958197715</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AI33" t="n">
         <v>3508749.9</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AJ33" t="n">
         <v>33.91670919605868</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AK33" t="n">
         <v>45.1885755664717</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AL33" t="n">
         <v>4</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
       <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
         <v>5.72</v>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AT33" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP33" t="n">
+      <c r="AU33" t="n">
         <v>6.23</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AV33" t="n">
         <v>8.93</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AW33" t="n">
         <v>13.2897521039921</v>
       </c>
     </row>
@@ -4800,79 +4985,84 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
         <v>8.190248938447064</v>
       </c>
-      <c r="V34" t="n">
+      <c r="AA34" t="n">
         <v>2.779081806547867</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AB34" t="n">
         <v>9.191675674747879</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AC34" t="n">
         <v>10.08965558363613</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AD34" t="n">
         <v>2.865555555555555</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AE34" t="n">
         <v>4793.374304222222</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AF34" t="n">
         <v>-3.954353082349182</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AG34" t="n">
         <v>10.08965558363613</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AH34" t="n">
         <v>7.016322250302792</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AI34" t="n">
         <v>3406426.6</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AJ34" t="n">
         <v>35.00376318104139</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AK34" t="n">
         <v>46.41580711000788</v>
       </c>
-      <c r="AG34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
       <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
       <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="n">
         <v>5.1</v>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="AT34" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP34" t="n">
+      <c r="AU34" t="n">
         <v>5.72</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AV34" t="n">
         <v>7.5</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AW34" t="n">
         <v>12.00719132972217</v>
       </c>
     </row>
@@ -4932,79 +5122,84 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.78610923392749</v>
       </c>
-      <c r="V35" t="n">
+      <c r="AA35" t="n">
         <v>-1.740511069588535</v>
       </c>
-      <c r="W35" t="n">
+      <c r="AB35" t="n">
         <v>-2.213207452270327</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AC35" t="n">
         <v>9.646179163555789</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AD35" t="n">
         <v>2.065913978494624</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AE35" t="n">
         <v>4361.682420333333</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AF35" t="n">
         <v>-17.34615518627135</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AG35" t="n">
         <v>9.646179163555789</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AH35" t="n">
         <v>6.172845830222457</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AI35" t="n">
         <v>3381041.2</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AJ35" t="n">
         <v>32.21065747438984</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AK35" t="n">
         <v>45.63941131507063</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AL35" t="n">
         <v>2</v>
       </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="inlineStr"/>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
       <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="n">
         <v>4.3</v>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AT35" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP35" t="n">
+      <c r="AU35" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AV35" t="n">
         <v>6.46</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AW35" t="n">
         <v>8.764409462889567</v>
       </c>
     </row>
@@ -5064,79 +5259,84 @@
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
         <v>-1.72817294556874</v>
       </c>
-      <c r="V36" t="n">
+      <c r="AA36" t="n">
         <v>-5.089827755510401</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AB36" t="n">
         <v>-7.087678502646333</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AC36" t="n">
         <v>10.40079043222437</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AD36" t="n">
         <v>-0.6786021505376327</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AE36" t="n">
         <v>4516.561138999999</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AF36" t="n">
         <v>-7.452666039830635</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AG36" t="n">
         <v>10.40079043222437</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
         <v>4.564123765557706</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AI36" t="n">
         <v>3532631.6</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AJ36" t="n">
         <v>32.00942039922872</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AK36" t="n">
         <v>42.87235045964034</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AL36" t="n">
         <v>3</v>
       </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
       <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="n">
         <v>3.26</v>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AT36" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP36" t="n">
+      <c r="AU36" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AV36" t="n">
         <v>6.23</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AW36" t="n">
         <v>7.104158352677037</v>
       </c>
     </row>
@@ -5196,79 +5396,84 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
         <v>-0.8135439402883526</v>
       </c>
-      <c r="V37" t="n">
+      <c r="AA37" t="n">
         <v>-8.775033745258142</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AB37" t="n">
         <v>-2.614661574337707</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AC37" t="n">
         <v>8.863988283975676</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AD37" t="n">
         <v>-1.56032258064516</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AE37" t="n">
         <v>3651.065773333334</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AF37" t="n">
         <v>-17.99191958325197</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AG37" t="n">
         <v>8.863988283975676</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AH37" t="n">
         <v>2.193988283975677</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AI37" t="n">
         <v>3512440.2</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AJ37" t="n">
         <v>33.60543761001255</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AK37" t="n">
         <v>42.6176764518297</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AL37" t="n">
         <v>4</v>
       </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
       <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="n">
         <v>2.94</v>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AT37" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP37" t="n">
+      <c r="AU37" t="n">
         <v>3.26</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AV37" t="n">
         <v>5.72</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AW37" t="n">
         <v>6.131347384614783</v>
       </c>
     </row>
@@ -5328,79 +5533,84 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-42.36494734259914</v>
       </c>
-      <c r="V38" t="n">
+      <c r="AA38" t="n">
         <v>-23.71262721854784</v>
       </c>
-      <c r="W38" t="n">
+      <c r="AB38" t="n">
         <v>-40.29777148094308</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AC38" t="n">
         <v>12.31920706109511</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AD38" t="n">
         <v>-2.349677419354839</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AE38" t="n">
         <v>2226.407810666667</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AF38" t="n">
         <v>-53.55238983307551</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AG38" t="n">
         <v>12.31920706109511</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AH38" t="n">
         <v>5.745873727761773</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AI38" t="n">
         <v>2661511.5</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AJ38" t="n">
         <v>25.82094422661709</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AK38" t="n">
         <v>39.84931119027665</v>
       </c>
-      <c r="AG38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
       <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AT38" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP38" t="n">
+      <c r="AU38" t="n">
         <v>2.94</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AV38" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AW38" t="n">
         <v>6.186377293058576</v>
       </c>
     </row>
@@ -5460,79 +5670,84 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-2.228995470938311</v>
       </c>
-      <c r="V39" t="n">
+      <c r="AA39" t="n">
         <v>-3.988524797773596</v>
       </c>
-      <c r="W39" t="n">
+      <c r="AB39" t="n">
         <v>-16.64516974413968</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AC39" t="n">
         <v>12.17640495793575</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AD39" t="n">
         <v>-2.896666666666667</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AE39" t="n">
         <v>3195.712981111111</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AF39" t="n">
         <v>-26.73210304782151</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AG39" t="n">
         <v>12.17640495793575</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AH39" t="n">
         <v>5.279738291269081</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AI39" t="n">
         <v>3209692.4</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AJ39" t="n">
         <v>33.17391411089736</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AK39" t="n">
         <v>42.85409405586654</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AL39" t="n">
         <v>2</v>
       </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM39" t="inlineStr"/>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
       <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="n">
         <v>-5.84</v>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AT39" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP39" t="n">
+      <c r="AU39" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AV39" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AW39" t="n">
         <v>5.146224512525066</v>
       </c>
     </row>
@@ -5592,79 +5807,84 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
         <v>4.208697946868134</v>
       </c>
-      <c r="V40" t="n">
+      <c r="AA40" t="n">
         <v>-6.42719595567115</v>
       </c>
-      <c r="W40" t="n">
+      <c r="AB40" t="n">
         <v>-3.993652770907252</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AC40" t="n">
         <v>12.40363992150963</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AD40" t="n">
         <v>-2.376666666666666</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AE40" t="n">
         <v>3266.704911666666</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AF40" t="n">
         <v>-27.67274014163042</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AG40" t="n">
         <v>12.40363992150963</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AH40" t="n">
         <v>6.026973254842969</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AI40" t="n">
         <v>3583773.5</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AJ40" t="n">
         <v>32.88058801707195</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AK40" t="n">
         <v>40.09277092985927</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AL40" t="n">
         <v>3</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM40" t="inlineStr"/>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
       <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="n">
         <v>1.78</v>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AT40" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP40" t="n">
+      <c r="AU40" t="n">
         <v>-5.84</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AV40" t="n">
         <v>3.26</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AW40" t="n">
         <v>6.027607325443429</v>
       </c>
     </row>
@@ -5724,79 +5944,84 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
         <v>13.2110593373659</v>
       </c>
-      <c r="V41" t="n">
+      <c r="AA41" t="n">
         <v>6.379887179004173</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AB41" t="n">
         <v>13.30458006689888</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AC41" t="n">
         <v>12.17034968442652</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AD41" t="n">
         <v>-0.8700000000000001</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AE41" t="n">
         <v>4432.940711333334</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AF41" t="n">
         <v>21.41497816091567</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AG41" t="n">
         <v>12.17034968442652</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AH41" t="n">
         <v>7.300349684426519</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AI41" t="n">
         <v>3827029.2</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AJ41" t="n">
         <v>34.91769542808819</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AK41" t="n">
         <v>43.05435401433571</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AL41" t="n">
         <v>4</v>
       </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM41" t="inlineStr"/>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
       <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="n">
         <v>3.29</v>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AT41" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP41" t="n">
+      <c r="AU41" t="n">
         <v>1.78</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AV41" t="n">
         <v>2.94</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AW41" t="n">
         <v>5.579559218087171</v>
       </c>
     </row>
@@ -5856,79 +6081,84 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
         <v>66.5234535177148</v>
       </c>
-      <c r="V42" t="n">
+      <c r="AA42" t="n">
         <v>46.47504144241408</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AB42" t="n">
         <v>45.13112955321681</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AC42" t="n">
         <v>10.70917123775022</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AD42" t="n">
         <v>-1.596666666666667</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AE42" t="n">
         <v>5077.564255555556</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AF42" t="n">
         <v>128.0608355409583</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AG42" t="n">
         <v>10.70917123775022</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AH42" t="n">
         <v>5.112504571083549</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AI42" t="n">
         <v>3377295.100000001</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AJ42" t="n">
         <v>33.88495130318934</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AK42" t="n">
         <v>45.78994888542609</v>
       </c>
-      <c r="AG42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
       <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1</v>
+      </c>
       <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="n">
         <v>22.63</v>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AT42" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP42" t="n">
+      <c r="AU42" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AV42" t="n">
         <v>-23.13</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AW42" t="n">
         <v>5.818790729730394</v>
       </c>
     </row>
@@ -5988,79 +6218,84 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
         <v>15.299198726949</v>
       </c>
-      <c r="V43" t="n">
+      <c r="AA43" t="n">
         <v>25.39220425950273</v>
       </c>
-      <c r="W43" t="n">
+      <c r="AB43" t="n">
         <v>26.84168984466506</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AC43" t="n">
         <v>9.337915541986884</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AD43" t="n">
         <v>-1.079999999999999</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AE43" t="n">
         <v>5443.51475</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AF43" t="n">
         <v>70.33803668148433</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AG43" t="n">
         <v>9.337915541986884</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AH43" t="n">
         <v>4.257915541986885</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AI43" t="n">
         <v>3625478.1</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AJ43" t="n">
         <v>33.86266489928597</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AK43" t="n">
         <v>47.85230119028991</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AL43" t="n">
         <v>2</v>
       </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="inlineStr"/>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
       <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AT43" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP43" t="n">
+      <c r="AU43" t="n">
         <v>22.63</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AV43" t="n">
         <v>-5.84</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AW43" t="n">
         <v>6.671182051341229</v>
       </c>
     </row>
@@ -6120,79 +6355,84 @@
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
         <v>3.596743897353449</v>
       </c>
-      <c r="V44" t="n">
+      <c r="AA44" t="n">
         <v>28.13969126073221</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AB44" t="n">
         <v>19.99142574024248</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AC44" t="n">
         <v>11.40194927174409</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AD44" t="n">
         <v>-1.016666666666667</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AE44" t="n">
         <v>5963.277718666666</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AF44" t="n">
         <v>82.5471807193082</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AG44" t="n">
         <v>11.40194927174409</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AH44" t="n">
         <v>6.385282605077427</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AI44" t="n">
         <v>3896581.3</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AJ44" t="n">
         <v>31.32870857846595</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AK44" t="n">
         <v>45.62916985717711</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AL44" t="n">
         <v>3</v>
       </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="inlineStr"/>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
       <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="n">
         <v>5.53</v>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AT44" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP44" t="n">
+      <c r="AU44" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AV44" t="n">
         <v>1.78</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AW44" t="n">
         <v>9.813660365087728</v>
       </c>
     </row>
@@ -6252,79 +6492,84 @@
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>6.370211591558372</v>
       </c>
-      <c r="V45" t="n">
+      <c r="AA45" t="n">
         <v>22.5491693350361</v>
       </c>
-      <c r="W45" t="n">
+      <c r="AB45" t="n">
         <v>6.882582051715769</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AC45" t="n">
         <v>8.751331328013734</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AD45" t="n">
         <v>-2.343333333333334</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AE45" t="n">
         <v>7545.291487555555</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AF45" t="n">
         <v>70.20961882628231</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AG45" t="n">
         <v>8.751331328013734</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AH45" t="n">
         <v>2.4079979946804</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AI45" t="n">
         <v>4177237.5</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AJ45" t="n">
         <v>34.02813941031603</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AK45" t="n">
         <v>44.94689133667885</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AL45" t="n">
         <v>4</v>
       </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
       <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="n">
         <v>4.45</v>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AT45" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP45" t="n">
+      <c r="AU45" t="n">
         <v>5.53</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AV45" t="n">
         <v>3.29</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AW45" t="n">
         <v>8.601347091664913</v>
       </c>
     </row>
@@ -6383,82 +6628,97 @@
         <v>3802769.071241618</v>
       </c>
       <c r="R46" t="n">
-        <v>6159720.427422995</v>
+        <v>6162846</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3447869</v>
       </c>
       <c r="U46" t="n">
+        <v>731465</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1994295</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1552120</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1645711</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
         <v>16.00151451229943</v>
       </c>
-      <c r="V46" t="n">
+      <c r="AA46" t="n">
         <v>15.75395331097709</v>
       </c>
-      <c r="W46" t="n">
+      <c r="AB46" t="n">
         <v>24.06931511783677</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AC46" t="n">
         <v>7.794917877998508</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AD46" t="n">
         <v>-2.898458781362008</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AE46" t="n">
         <v>8764.095763444446</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AF46" t="n">
         <v>72.60432999651979</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AG46" t="n">
         <v>7.794917877998508</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AH46" t="n">
         <v>0.5149178779985082</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AI46" t="n">
         <v>3873955.5</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AJ46" t="n">
         <v>34.26769615706738</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AK46" t="n">
         <v>47.84110452481966</v>
       </c>
-      <c r="AG46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
       <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
       <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="n">
         <v>13.49</v>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AT46" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP46" t="n">
+      <c r="AU46" t="n">
         <v>4.45</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AV46" t="n">
         <v>22.63</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AW46" t="n">
         <v>12.06898414518238</v>
       </c>
     </row>
@@ -6517,82 +6777,97 @@
         <v>3891250.725085199</v>
       </c>
       <c r="R47" t="n">
-        <v>6061356.994818534</v>
+        <v>6045123</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3425429</v>
       </c>
       <c r="U47" t="n">
+        <v>728397</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2063496</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1565703</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1742885</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
         <v>6.430973455292022</v>
       </c>
-      <c r="V47" t="n">
+      <c r="AA47" t="n">
         <v>8.390088652442573</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AB47" t="n">
         <v>14.00942578430813</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AC47" t="n">
         <v>8.643959541327151</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AD47" t="n">
         <v>-1.822616487455197</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AE47" t="n">
         <v>8036.527860888889</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AF47" t="n">
         <v>47.63490557068646</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AG47" t="n">
         <v>8.643959541327151</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AH47" t="n">
         <v>1.603959541327151</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AI47" t="n">
         <v>3837514.2</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AJ47" t="n">
         <v>34.04900755806975</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AK47" t="n">
         <v>50.2986256050857</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AL47" t="n">
         <v>2</v>
       </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="inlineStr"/>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
       <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="n">
         <v>5.96</v>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AT47" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP47" t="n">
+      <c r="AU47" t="n">
         <v>13.49</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AV47" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AW47" t="n">
         <v>15.26956166407503</v>
       </c>
     </row>
@@ -6651,82 +6926,97 @@
         <v>4057577.783186123</v>
       </c>
       <c r="R48" t="n">
-        <v>6819597.105406575</v>
+        <v>6828276</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4037218</v>
       </c>
       <c r="U48" t="n">
+        <v>707317</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2138326</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1557205</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1745456</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
         <v>6.728387810561487</v>
       </c>
-      <c r="V48" t="n">
+      <c r="AA48" t="n">
         <v>8.205039572031003</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AB48" t="n">
         <v>2.88041161451511</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AC48" t="n">
         <v>8.676519473763666</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AD48" t="n">
         <v>-0.1292473118279549</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AE48" t="n">
         <v>7279.794879555556</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AF48" t="n">
         <v>22.07707276097231</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AG48" t="n">
         <v>8.676519473763666</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AH48" t="n">
         <v>2.553186140430333</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AI48" t="n">
         <v>4088046.399999999</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AJ48" t="n">
         <v>31.87060939425737</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AK48" t="n">
         <v>45.84889251746262</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AL48" t="n">
         <v>3</v>
       </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="inlineStr"/>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
       <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="n">
         <v>4.84</v>
       </c>
-      <c r="AO48" t="inlineStr">
+      <c r="AT48" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP48" t="n">
+      <c r="AU48" t="n">
         <v>5.96</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AV48" t="n">
         <v>5.53</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AW48" t="n">
         <v>14.89166743732671</v>
       </c>
     </row>
@@ -6785,82 +7075,97 @@
         <v>4413315.796011902</v>
       </c>
       <c r="R49" t="n">
-        <v>7076952.634272937</v>
+        <v>7140756</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>4028336</v>
       </c>
       <c r="U49" t="n">
+        <v>766881</v>
+      </c>
+      <c r="V49" t="n">
+        <v>2256838</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1603694</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1828325</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
         <v>5.575522840912583</v>
       </c>
-      <c r="V49" t="n">
+      <c r="AA49" t="n">
         <v>9.402665677020261</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AB49" t="n">
         <v>-1.849416110505098</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AC49" t="n">
         <v>9.027303488048076</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AD49" t="n">
         <v>0.189166666666666</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AE49" t="n">
         <v>6677.770264888889</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AF49" t="n">
         <v>-11.49751767837556</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AG49" t="n">
         <v>9.027303488048076</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AH49" t="n">
         <v>2.820636821381409</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AI49" t="n">
         <v>4450584.2</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AJ49" t="n">
         <v>33.7189149235734</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AK49" t="n">
         <v>43.70874951652414</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AL49" t="n">
         <v>4</v>
       </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
       <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="n">
         <v>6.9</v>
       </c>
-      <c r="AO49" t="inlineStr">
+      <c r="AT49" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP49" t="n">
+      <c r="AU49" t="n">
         <v>4.84</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AV49" t="n">
         <v>4.45</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AW49" t="n">
         <v>15.0018830511869</v>
       </c>
     </row>
@@ -6919,86 +7224,101 @@
         <v>4170114.443535164</v>
       </c>
       <c r="R50" t="n">
-        <v>6565078.867856057</v>
+        <v>6568527</v>
       </c>
       <c r="S50" t="n">
-        <v>6.580792833200877</v>
+        <v>6.582689231566063</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>3689235</v>
       </c>
       <c r="U50" t="n">
+        <v>735348</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2152370</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1520821</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1727758</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="n">
         <v>8.440460158914931</v>
       </c>
-      <c r="V50" t="n">
+      <c r="AA50" t="n">
         <v>-6.986558027968403</v>
       </c>
-      <c r="W50" t="n">
+      <c r="AB50" t="n">
         <v>18.04302219856271</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AC50" t="n">
         <v>13.36118620621058</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AD50" t="n">
         <v>1.873333333333334</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AE50" t="n">
         <v>6437.572567777778</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AF50" t="n">
         <v>-26.54607227559894</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AG50" t="n">
         <v>13.36118620621058</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AH50" t="n">
         <v>8.734519539543918</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AI50" t="n">
         <v>3935031</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AJ50" t="n">
         <v>36.5832873997689</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AK50" t="n">
         <v>49.81097226425917</v>
       </c>
-      <c r="AG50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM50" t="n">
-        <v>-3.079207166799123</v>
+        <v>1</v>
       </c>
       <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>-3.077310768433937</v>
+      </c>
+      <c r="AS50" t="n">
         <v>9.66</v>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AT50" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP50" t="n">
+      <c r="AU50" t="n">
         <v>6.9</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AV50" t="n">
         <v>13.49</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AW50" t="n">
         <v>18.3810683044001</v>
       </c>
     </row>
@@ -7057,86 +7377,101 @@
         <v>4254805.793562238</v>
       </c>
       <c r="R51" t="n">
-        <v>6524194.743626461</v>
+        <v>6500703</v>
       </c>
       <c r="S51" t="n">
-        <v>7.63587673855175</v>
+        <v>7.536323082259866</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>3624281</v>
       </c>
       <c r="U51" t="n">
+        <v>727274</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2281915</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1545230</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1780045</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
         <v>11.71159822306986</v>
       </c>
-      <c r="V51" t="n">
+      <c r="AA51" t="n">
         <v>4.589515677491596</v>
       </c>
-      <c r="W51" t="n">
+      <c r="AB51" t="n">
         <v>14.29536001327434</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AC51" t="n">
         <v>11.53805080852743</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AD51" t="n">
         <v>0.07000000000000028</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AE51" t="n">
         <v>7163.454256000002</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AF51" t="n">
         <v>-10.86381606586405</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AG51" t="n">
         <v>11.53805080852743</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AH51" t="n">
         <v>5.108050808527434</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AI51" t="n">
         <v>4021156.500000001</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AJ51" t="n">
         <v>36.29959192088145</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AK51" t="n">
         <v>52.64257434397292</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AL51" t="n">
         <v>2</v>
       </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
       <c r="AM51" t="n">
-        <v>-1.70412326144825</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>-1.803676917740134</v>
+      </c>
+      <c r="AS51" t="n">
         <v>9.34</v>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP51" t="n">
+      <c r="AU51" t="n">
         <v>9.66</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AV51" t="n">
         <v>5.96</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AW51" t="n">
         <v>19.96408869322233</v>
       </c>
     </row>
@@ -7195,86 +7530,101 @@
         <v>4443638.242661299</v>
       </c>
       <c r="R52" t="n">
-        <v>7303045.372105934</v>
+        <v>7352703</v>
       </c>
       <c r="S52" t="n">
-        <v>7.089103054432377</v>
+        <v>7.680225579633859</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>4259708</v>
       </c>
       <c r="U52" t="n">
+        <v>714203</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2310132</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1575387</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1748844</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="n">
         <v>9.343631400246831</v>
       </c>
-      <c r="V52" t="n">
+      <c r="AA52" t="n">
         <v>2.950118842539085</v>
       </c>
-      <c r="W52" t="n">
+      <c r="AB52" t="n">
         <v>11.31244619409408</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AC52" t="n">
         <v>11.51935465158569</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AD52" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AE52" t="n">
         <v>6971.697782222222</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AF52" t="n">
         <v>-4.23222223195584</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AG52" t="n">
         <v>11.51935465158569</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AH52" t="n">
         <v>6.14935465158569</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AI52" t="n">
         <v>4277867</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AJ52" t="n">
         <v>33.30215969781202</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AK52" t="n">
         <v>46.97804536700182</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AL52" t="n">
         <v>3</v>
       </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
       <c r="AM52" t="n">
-        <v>-2.420896945567622</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>-1.829774420366141</v>
+      </c>
+      <c r="AS52" t="n">
         <v>9.51</v>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AT52" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP52" t="n">
+      <c r="AU52" t="n">
         <v>9.34</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AV52" t="n">
         <v>4.84</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AW52" t="n">
         <v>19.95280860197066</v>
       </c>
     </row>
@@ -7333,86 +7683,101 @@
         <v>4782032.468479682</v>
       </c>
       <c r="R53" t="n">
-        <v>7608447.949196015</v>
+        <v>7672424</v>
       </c>
       <c r="S53" t="n">
-        <v>7.510228517697048</v>
+        <v>7.44554218068787</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>4298016</v>
       </c>
       <c r="U53" t="n">
+        <v>779801</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2473101</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1707977</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1693140</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
         <v>6.04723684532309</v>
       </c>
-      <c r="V53" t="n">
+      <c r="AA53" t="n">
         <v>7.672107258236927</v>
       </c>
-      <c r="W53" t="n">
+      <c r="AB53" t="n">
         <v>11.35988918487037</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AC53" t="n">
         <v>11.61890430625601</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AD53" t="n">
         <v>1.486666666666667</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AE53" t="n">
         <v>6891.550958</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AF53" t="n">
         <v>3.201378373783692</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AG53" t="n">
         <v>11.61890430625601</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AH53" t="n">
         <v>6.605570972922673</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AI53" t="n">
         <v>4692563.199999999</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AJ53" t="n">
         <v>33.91406427941131</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="AK53" t="n">
         <v>45.38101905585417</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AL53" t="n">
         <v>4</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
       <c r="AM53" t="n">
-        <v>-0.8397714823029512</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>-0.90445781931213</v>
+      </c>
+      <c r="AS53" t="n">
         <v>8.35</v>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AT53" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP53" t="n">
+      <c r="AU53" t="n">
         <v>9.51</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AV53" t="n">
         <v>6.9</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AW53" t="n">
         <v>20.16000846400059</v>
       </c>
     </row>
@@ -7471,86 +7836,101 @@
         <v>4441663.946155024</v>
       </c>
       <c r="R54" t="n">
-        <v>7054578.789528189</v>
+        <v>7061843</v>
       </c>
       <c r="S54" t="n">
-        <v>7.456116392886325</v>
+        <v>7.510298732120613</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>3911568</v>
       </c>
       <c r="U54" t="n">
+        <v>783842</v>
+      </c>
+      <c r="V54" t="n">
+        <v>2361461</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1612050</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1873238</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
         <v>6.650126006928359</v>
       </c>
-      <c r="V54" t="n">
+      <c r="AA54" t="n">
         <v>8.292078154667792</v>
       </c>
-      <c r="W54" t="n">
+      <c r="AB54" t="n">
         <v>-1.556099321210525</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AC54" t="n">
         <v>10.10195024932521</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AD54" t="n">
         <v>1.596666666666667</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AE54" t="n">
         <v>7062.786664333333</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AF54" t="n">
         <v>9.711954156213508</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AG54" t="n">
         <v>10.10195024932521</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AH54" t="n">
         <v>5.198616915991876</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AI54" t="n">
         <v>4311041</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AJ54" t="n">
         <v>35.61312685265577</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AK54" t="n">
         <v>46.69163434075436</v>
       </c>
-      <c r="AG54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.9461163928863252</v>
+        <v>1</v>
       </c>
       <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.000298732120613</v>
+      </c>
+      <c r="AS54" t="n">
         <v>6.51</v>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AT54" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP54" t="n">
+      <c r="AU54" t="n">
         <v>8.35</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AV54" t="n">
         <v>9.66</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AW54" t="n">
         <v>17.39682608410902</v>
       </c>
     </row>
@@ -7609,86 +7989,101 @@
         <v>4493586.559883779</v>
       </c>
       <c r="R55" t="n">
-        <v>6953869.983724036</v>
+        <v>6975107</v>
       </c>
       <c r="S55" t="n">
-        <v>6.585873919801788</v>
+        <v>7.297733798944517</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>3855569</v>
       </c>
       <c r="U55" t="n">
+        <v>763991</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2484274</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1561036</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1870334</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="n">
         <v>6.70290150455235</v>
       </c>
-      <c r="V55" t="n">
+      <c r="AA55" t="n">
         <v>3.026878745606587</v>
       </c>
-      <c r="W55" t="n">
+      <c r="AB55" t="n">
         <v>1.042710081260312</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AC55" t="n">
         <v>10.42373724508627</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AD55" t="n">
         <v>2.253333333333333</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AE55" t="n">
         <v>6688.188597333333</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AF55" t="n">
         <v>-6.634587751692466</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AG55" t="n">
         <v>10.42373724508627</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AH55" t="n">
         <v>6.177070578419605</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AI55" t="n">
         <v>4304356.3</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AJ55" t="n">
         <v>36.18434654212989</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AK55" t="n">
         <v>50.13544069295565</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AL55" t="n">
         <v>2</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
       <c r="AM55" t="n">
-        <v>0.9758739198017876</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.687733798944516</v>
+      </c>
+      <c r="AS55" t="n">
         <v>5.61</v>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AT55" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP55" t="n">
+      <c r="AU55" t="n">
         <v>6.51</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AV55" t="n">
         <v>9.34</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AW55" t="n">
         <v>13.02684232700213</v>
       </c>
     </row>
@@ -7747,86 +8142,101 @@
         <v>4726541.829827959</v>
       </c>
       <c r="R56" t="n">
-        <v>7840573.245748451</v>
+        <v>7898065</v>
       </c>
       <c r="S56" t="n">
-        <v>7.360324991209977</v>
+        <v>7.417163456758691</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>4552327</v>
       </c>
       <c r="U56" t="n">
+        <v>782448</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2469966</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1704853</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1837835</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
         <v>5.23031335818811</v>
       </c>
-      <c r="V56" t="n">
+      <c r="AA56" t="n">
         <v>10.80198115326656</v>
       </c>
-      <c r="W56" t="n">
+      <c r="AB56" t="n">
         <v>-2.067296627697379</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AC56" t="n">
         <v>9.033767617571421</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AD56" t="n">
         <v>0.8633333333333333</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AE56" t="n">
         <v>6301.844620444444</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AF56" t="n">
         <v>-9.608178419407388</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AG56" t="n">
         <v>9.033767617571421</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AH56" t="n">
         <v>3.397100950904754</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AI56" t="n">
         <v>4722716.2</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AJ56" t="n">
         <v>31.74305286436648</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AK56" t="n">
         <v>44.2463449317577</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AL56" t="n">
         <v>3</v>
       </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
       <c r="AM56" t="n">
-        <v>0.9903249912099765</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.047163456758691</v>
+      </c>
+      <c r="AS56" t="n">
         <v>6.37</v>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AT56" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP56" t="n">
+      <c r="AU56" t="n">
         <v>5.61</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AV56" t="n">
         <v>9.51</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AW56" t="n">
         <v>11.1583746011608</v>
       </c>
     </row>
@@ -7885,86 +8295,101 @@
         <v>5135163.108031793</v>
       </c>
       <c r="R57" t="n">
-        <v>8139597.501671606</v>
+        <v>8180413</v>
       </c>
       <c r="S57" t="n">
-        <v>6.981049959495578</v>
+        <v>6.620971416595323</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>4572118</v>
       </c>
       <c r="U57" t="n">
+        <v>822513</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2660321</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1781951</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1767477</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
         <v>9.407285444637559</v>
       </c>
-      <c r="V57" t="n">
+      <c r="AA57" t="n">
         <v>3.851762950021231</v>
       </c>
-      <c r="W57" t="n">
+      <c r="AB57" t="n">
         <v>-12.67180548452658</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AC57" t="n">
         <v>9.409550124407385</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AD57" t="n">
         <v>2.614523809523811</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AE57" t="n">
         <v>6569.430029333333</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AF57" t="n">
         <v>-4.674142738402532</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AG57" t="n">
         <v>9.409550124407385</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AH57" t="n">
         <v>5.672883457740719</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AI57" t="n">
         <v>5160987.6</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AJ57" t="n">
         <v>33.73676193292928</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AK57" t="n">
         <v>39.46831416529658</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AL57" t="n">
         <v>4</v>
       </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
       <c r="AM57" t="n">
-        <v>-0.3989500405044222</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>-0.7590285834046773</v>
+      </c>
+      <c r="AS57" t="n">
         <v>7.38</v>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AT57" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP57" t="n">
+      <c r="AU57" t="n">
         <v>6.37</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AV57" t="n">
         <v>8.35</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AW57" t="n">
         <v>11.02598785965252</v>
       </c>
     </row>
@@ -8023,86 +8448,101 @@
         <v>4788623.361407248</v>
       </c>
       <c r="R58" t="n">
-        <v>7535572.354430312</v>
+        <v>7546230</v>
       </c>
       <c r="S58" t="n">
-        <v>6.818175531841941</v>
+        <v>6.859215080255954</v>
       </c>
       <c r="T58" t="n">
-        <v>1</v>
+        <v>4176184</v>
       </c>
       <c r="U58" t="n">
+        <v>819411</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2497280</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1708025</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1972239</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
         <v>7.819277904951916</v>
       </c>
-      <c r="V58" t="n">
+      <c r="AA58" t="n">
         <v>6.329413873184042</v>
       </c>
-      <c r="W58" t="n">
+      <c r="AB58" t="n">
         <v>10.87757853879581</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AC58" t="n">
         <v>9.458110952394904</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AD58" t="n">
         <v>3.19</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AE58" t="n">
         <v>5818.067809555556</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AF58" t="n">
         <v>-17.62362243027297</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AG58" t="n">
         <v>9.458110952394904</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AH58" t="n">
         <v>6.76477761906157</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AI58" t="n">
         <v>4579756.300000001</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AJ58" t="n">
         <v>36.14484028331376</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AK58" t="n">
         <v>47.82306866415576</v>
       </c>
-      <c r="AG58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM58" t="n">
-        <v>-0.9918244681580584</v>
+        <v>1</v>
       </c>
       <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>-0.9507849197440459</v>
+      </c>
+      <c r="AS58" t="n">
         <v>7.81</v>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AT58" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP58" t="n">
+      <c r="AU58" t="n">
         <v>7.38</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AV58" t="n">
         <v>6.51</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AW58" t="n">
         <v>9.476302029641426</v>
       </c>
     </row>
@@ -8161,86 +8601,101 @@
         <v>4863340.166303576</v>
       </c>
       <c r="R59" t="n">
-        <v>7534422.709761673</v>
+        <v>7541258</v>
       </c>
       <c r="S59" t="n">
-        <v>8.348627848902201</v>
+        <v>8.116735700255218</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>4101561</v>
       </c>
       <c r="U59" t="n">
+        <v>797413</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2663617</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1713049</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1964085</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" t="n">
         <v>7.333911095656176</v>
       </c>
-      <c r="V59" t="n">
+      <c r="AA59" t="n">
         <v>5.585101474270227</v>
       </c>
-      <c r="W59" t="n">
+      <c r="AB59" t="n">
         <v>12.75204768450591</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AC59" t="n">
         <v>9.231437233294981</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AD59" t="n">
         <v>3.793333333333333</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AE59" t="n">
         <v>6022.068182222222</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AF59" t="n">
         <v>-9.959653580592832</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AG59" t="n">
         <v>9.231437233294981</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AH59" t="n">
         <v>7.524770566628314</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AI59" t="n">
         <v>4514543.4</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AJ59" t="n">
         <v>37.02985998539742</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AK59" t="n">
         <v>52.32284177398759</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AL59" t="n">
         <v>2</v>
       </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
       <c r="AM59" t="n">
-        <v>0.1186278489022001</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>-0.1132642997447828</v>
+      </c>
+      <c r="AS59" t="n">
         <v>8.23</v>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AT59" t="inlineStr">
         <is>
           <t>2011-12 base</t>
         </is>
       </c>
-      <c r="AP59" t="n">
+      <c r="AU59" t="n">
         <v>7.81</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AV59" t="n">
         <v>5.61</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AW59" t="n">
         <v>10.3813332654406</v>
       </c>
     </row>
@@ -8283,72 +8738,97 @@
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>8464935.170072669</v>
+        <v>8502278</v>
       </c>
       <c r="S60" t="n">
-        <v>7.963217799958411</v>
+        <v>7.65013962280634</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+        <v>4917427</v>
+      </c>
+      <c r="U60" t="n">
+        <v>837237</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2675826</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1810390</v>
+      </c>
       <c r="X60" t="n">
+        <v>1966531</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>8.334527681757553</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>6.190387089092142</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>7.002587283406836</v>
+      </c>
+      <c r="AC60" t="n">
         <v>12.11115462536545</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AD60" t="n">
         <v>4.664086021505375</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AE60" t="n">
         <v>5669.842256</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AF60" t="n">
         <v>-10.02884714729559</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AG60" t="n">
         <v>12.11115462536545</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AH60" t="n">
         <v>11.34782129203212</v>
       </c>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="n">
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="n">
+        <v>32.33880997767921</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>45.64614086256212</v>
+      </c>
+      <c r="AL60" t="n">
         <v>3</v>
       </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="inlineStr"/>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
       <c r="AN60" t="n">
-        <v>7.963217799958411</v>
-      </c>
-      <c r="AO60" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="n">
+        <v>7.65013962280634</v>
+      </c>
+      <c r="AT60" t="inlineStr">
         <is>
           <t>2022-23 base (spliced)</t>
         </is>
       </c>
-      <c r="AP60" t="n">
+      <c r="AU60" t="n">
         <v>8.23</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AV60" t="n">
         <v>6.37</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AW60" t="n">
         <v>9.302904820121238</v>
       </c>
     </row>
@@ -8391,72 +8871,97 @@
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>8777104.006743735</v>
+        <v>8880334</v>
       </c>
       <c r="S61" t="n">
-        <v>7.832162523284558</v>
+        <v>8.556059455677856</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+        <v>4913735</v>
+      </c>
+      <c r="U61" t="n">
+        <v>885951</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2940719</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1852044</v>
+      </c>
       <c r="X61" t="n">
+        <v>1782106</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>10.54000626240217</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.933497610203651</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.8276769655277016</v>
+      </c>
+      <c r="AC61" t="n">
         <v>10.65310701519588</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AD61" t="n">
         <v>2.13</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AE61" t="n">
         <v>7333.314248222222</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AF61" t="n">
         <v>11.62786140468883</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AG61" t="n">
         <v>10.65310701519588</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AH61" t="n">
         <v>7.533107015195885</v>
       </c>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="n">
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="n">
+        <v>33.3780307985739</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>41.24867783240675</v>
+      </c>
+      <c r="AL61" t="n">
         <v>4</v>
       </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="inlineStr"/>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
       <c r="AN61" t="n">
-        <v>7.832162523284558</v>
-      </c>
-      <c r="AO61" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="n">
+        <v>8.556059455677856</v>
+      </c>
+      <c r="AT61" t="inlineStr">
         <is>
           <t>2022-23 base (spliced)</t>
         </is>
       </c>
-      <c r="AP61" t="n">
-        <v>7.963217799958411</v>
-      </c>
-      <c r="AQ61" t="n">
+      <c r="AU61" t="n">
+        <v>7.65013962280634</v>
+      </c>
+      <c r="AV61" t="n">
         <v>7.38</v>
       </c>
-      <c r="AR61" t="n">
+      <c r="AW61" t="n">
         <v>17.07920091983608</v>
       </c>
     </row>
@@ -8474,7 +8979,9 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>5.25</v>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
@@ -8490,63 +8997,94 @@
         <v>31163977.2819288</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>8136153</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7.817453218362025</v>
+      </c>
       <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+        <v>4474278</v>
+      </c>
+      <c r="U62" t="n">
+        <v>854877</v>
+      </c>
+      <c r="V62" t="n">
+        <v>2795605</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1913790</v>
+      </c>
       <c r="X62" t="n">
+        <v>1950544</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>11.94599724500256</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>12.04695481623512</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>-1.100018811107584</v>
+      </c>
+      <c r="AC62" t="n">
         <v>10.39133638585295</v>
       </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="n">
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
         <v>9767.271981833333</v>
       </c>
-      <c r="AA62" t="n">
+      <c r="AF62" t="n">
         <v>67.87827680164935</v>
       </c>
-      <c r="AB62" t="n">
+      <c r="AG62" t="n">
         <v>10.39133638585295</v>
       </c>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>34.5648235176878</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>47.77857484279809</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>7.832162523284558</v>
+        <v>0</v>
       </c>
       <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="n">
+        <v>7.817453218362025</v>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>2022-23 base (spliced)</t>
+        </is>
+      </c>
+      <c r="AU62" t="n">
+        <v>8.556059455677856</v>
+      </c>
+      <c r="AV62" t="n">
         <v>7.81</v>
       </c>
-      <c r="AR62" t="n">
+      <c r="AW62" t="n">
         <v>16.38629288719908</v>
       </c>
     </row>
@@ -8576,14 +9114,14 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
@@ -8591,36 +9129,118 @@
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="n">
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="n">
         <v>2</v>
       </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr">
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="n">
+      <c r="AU63" t="n">
+        <v>7.817453218362025</v>
+      </c>
+      <c r="AV63" t="n">
         <v>8.23</v>
       </c>
-      <c r="AR63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-27 Q3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="n">
+        <v>7.65013962280634</v>
+      </c>
+      <c r="AW64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/composite_master_quarterly.xlsx
+++ b/data/processed/composite_master_quarterly.xlsx
@@ -1022,7 +1022,7 @@
         <v>8.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.78</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -1055,7 +1055,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>0.7199999999999998</v>
+        <v>-0.1199999999999992</v>
       </c>
       <c r="AE5" t="n">
         <v>5957.187441333333</v>
@@ -1137,7 +1137,7 @@
         <v>8.088888888888889</v>
       </c>
       <c r="K6" t="n">
-        <v>9.903333333333334</v>
+        <v>10.18333333333333</v>
       </c>
       <c r="L6" t="n">
         <v>2.2</v>
@@ -1180,7 +1180,7 @@
         <v>15.82326235219023</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.814444444444446</v>
+        <v>-2.094444444444443</v>
       </c>
       <c r="AE6" t="n">
         <v>5865.912661111111</v>
@@ -1192,7 +1192,7 @@
         <v>15.82326235219023</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.919929018856893</v>
+        <v>5.639929018856895</v>
       </c>
       <c r="AI6" t="n">
         <v>2072727.7</v>
@@ -1270,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>10.02666666666667</v>
+        <v>9.873333333333333</v>
       </c>
       <c r="L7" t="n">
         <v>0.1333333333333333</v>
@@ -1313,7 +1313,7 @@
         <v>13.63341342336888</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.026666666666666</v>
+        <v>-1.873333333333333</v>
       </c>
       <c r="AE7" t="n">
         <v>6052.851920444445</v>
@@ -1325,7 +1325,7 @@
         <v>13.63341342336888</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.606746756702213</v>
+        <v>3.760080090035546</v>
       </c>
       <c r="AI7" t="n">
         <v>2185184.4</v>
@@ -1405,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>9.763333333333334</v>
+        <v>10.07</v>
       </c>
       <c r="L8" t="n">
         <v>3.033333333333333</v>
@@ -1448,7 +1448,7 @@
         <v>11.24888299217723</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.763333333333334</v>
+        <v>-2.07</v>
       </c>
       <c r="AE8" t="n">
         <v>5961.101261111111</v>
@@ -1460,7 +1460,7 @@
         <v>11.24888299217723</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.485549658843899</v>
+        <v>1.178882992177233</v>
       </c>
       <c r="AI8" t="n">
         <v>2128943.1</v>
@@ -1540,7 +1540,7 @@
         <v>7.790322580645161</v>
       </c>
       <c r="K9" t="n">
-        <v>9.896666666666667</v>
+        <v>10.69666666666667</v>
       </c>
       <c r="L9" t="n">
         <v>7.933333333333333</v>
@@ -1583,7 +1583,7 @@
         <v>13.91723013647719</v>
       </c>
       <c r="AD9" t="n">
-        <v>-2.106344086021505</v>
+        <v>-2.906344086021506</v>
       </c>
       <c r="AE9" t="n">
         <v>6093.205149777778</v>
@@ -1595,7 +1595,7 @@
         <v>13.91723013647719</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.02056346981052</v>
+        <v>3.22056346981052</v>
       </c>
       <c r="AI9" t="n">
         <v>2323049.3</v>
@@ -1675,7 +1675,7 @@
         <v>7.338709677419355</v>
       </c>
       <c r="K10" t="n">
-        <v>8.81</v>
+        <v>9.523333333333333</v>
       </c>
       <c r="L10" t="n">
         <v>1.1</v>
@@ -1718,7 +1718,7 @@
         <v>12.69099146058279</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.471290322580646</v>
+        <v>-2.184623655913978</v>
       </c>
       <c r="AE10" t="n">
         <v>5736.900974888889</v>
@@ -1730,7 +1730,7 @@
         <v>12.69099146058279</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.88099146058279</v>
+        <v>3.167658127249457</v>
       </c>
       <c r="AI10" t="n">
         <v>2272050.6</v>
@@ -1812,7 +1812,7 @@
         <v>7.280555555555556</v>
       </c>
       <c r="K11" t="n">
-        <v>10.09</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="L11" t="n">
         <v>4.8</v>
@@ -1855,7 +1855,7 @@
         <v>13.0042499150413</v>
       </c>
       <c r="AD11" t="n">
-        <v>-2.809444444444444</v>
+        <v>-2.38611111111111</v>
       </c>
       <c r="AE11" t="n">
         <v>6863.803933666666</v>
@@ -1867,7 +1867,7 @@
         <v>13.0042499150413</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.914249915041299</v>
+        <v>3.337583248374633</v>
       </c>
       <c r="AI11" t="n">
         <v>2318883.3</v>
@@ -1949,7 +1949,7 @@
         <v>7.674731182795699</v>
       </c>
       <c r="K12" t="n">
-        <v>10.59333333333333</v>
+        <v>10.4</v>
       </c>
       <c r="L12" t="n">
         <v>3.033333333333333</v>
@@ -1992,7 +1992,7 @@
         <v>14.80433839943327</v>
       </c>
       <c r="AD12" t="n">
-        <v>-2.918602150537635</v>
+        <v>-2.725268817204301</v>
       </c>
       <c r="AE12" t="n">
         <v>6776.804489666667</v>
@@ -2004,7 +2004,7 @@
         <v>14.80433839943327</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.211005066099936</v>
+        <v>4.40433839943327</v>
       </c>
       <c r="AI12" t="n">
         <v>2437481</v>
@@ -2226,7 +2226,7 @@
         <v>7.859999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>5.633333333333334</v>
+        <v>5.633333333333333</v>
       </c>
       <c r="M14" t="n">
         <v>59.79743333333334</v>
@@ -3870,7 +3870,7 @@
         <v>2.21</v>
       </c>
       <c r="L26" t="n">
-        <v>1.933333333333334</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="M26" t="n">
         <v>64.45829999999999</v>
@@ -5103,7 +5103,7 @@
         <v>3.473333333333333</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.3666666666666665</v>
+        <v>-0.3666666666666664</v>
       </c>
       <c r="M35" t="n">
         <v>70.42923333333333</v>
@@ -5511,7 +5511,7 @@
         <v>4.223655913978495</v>
       </c>
       <c r="K38" t="n">
-        <v>6.573333333333333</v>
+        <v>6.23</v>
       </c>
       <c r="L38" t="n">
         <v>-35.76666666666667</v>
@@ -5554,7 +5554,7 @@
         <v>12.31920706109511</v>
       </c>
       <c r="AD38" t="n">
-        <v>-2.349677419354839</v>
+        <v>-2.006344086021506</v>
       </c>
       <c r="AE38" t="n">
         <v>2226.407810666667</v>
@@ -5566,7 +5566,7 @@
         <v>12.31920706109511</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.745873727761773</v>
+        <v>6.089207061095106</v>
       </c>
       <c r="AI38" t="n">
         <v>2661511.5</v>
@@ -8852,7 +8852,7 @@
         <v>5.25</v>
       </c>
       <c r="K61" t="n">
-        <v>3.12</v>
+        <v>3.116666666666667</v>
       </c>
       <c r="L61" t="n">
         <v>4.766666666666667</v>
@@ -8907,7 +8907,7 @@
         <v>10.65310701519588</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.13</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="AE61" t="n">
         <v>7333.314248222222</v>
@@ -8919,7 +8919,7 @@
         <v>10.65310701519588</v>
       </c>
       <c r="AH61" t="n">
-        <v>7.533107015195885</v>
+        <v>7.536440348529217</v>
       </c>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="n">
@@ -8978,12 +8978,18 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J62" t="n">
         <v>5.25</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.233333333333334</v>
+      </c>
       <c r="M62" t="n">
         <v>94.57384999999999</v>
       </c>
@@ -9033,7 +9039,9 @@
       <c r="AC62" t="n">
         <v>10.39133638585295</v>
       </c>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>1.32</v>
+      </c>
       <c r="AE62" t="n">
         <v>9767.271981833333</v>
       </c>
@@ -9043,7 +9051,9 @@
       <c r="AG62" t="n">
         <v>10.39133638585295</v>
       </c>
-      <c r="AH62" t="inlineStr"/>
+      <c r="AH62" t="n">
+        <v>6.461336385852945</v>
+      </c>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="n">
         <v>34.5648235176878</v>
@@ -9101,10 +9111,16 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>4.635</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.7</v>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
@@ -9180,7 +9196,9 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
